--- a/templates/ERC000036/metadata_template_ERC000036.xlsx
+++ b/templates/ERC000036/metadata_template_ERC000036.xlsx
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$W$1:$W$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$W$1:$W$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="investigationtype">'cv_sample'!$N$1:$N$12</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="630">
   <si>
     <t>alias</t>
   </si>
@@ -448,6 +448,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -538,6 +541,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -973,7 +979,7 @@
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>sampling time point</t>
@@ -1201,9 +1207,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1222,6 +1225,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1423,6 +1429,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1432,9 +1441,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1474,7 +1480,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1543,6 +1549,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1618,6 +1627,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1639,6 +1651,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1684,6 +1699,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1696,6 +1714,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1705,9 +1726,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1732,6 +1750,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1792,10 +1813,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -2427,10 +2448,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2471,10 +2492,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2501,7 +2522,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2518,7 +2539,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2535,7 +2556,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2552,7 +2573,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2569,7 +2590,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2586,7 +2607,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2603,7 +2624,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2620,7 +2641,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2637,7 +2658,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2654,7 +2675,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2668,7 +2689,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2682,7 +2703,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2696,7 +2717,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2710,7 +2731,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2724,7 +2745,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2738,7 +2759,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2752,7 +2773,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2766,7 +2787,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2776,8 +2797,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2788,7 +2812,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2799,7 +2823,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -2810,7 +2834,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -2821,7 +2845,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -2832,7 +2856,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -2843,7 +2867,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -2854,7 +2878,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -2865,7 +2889,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -2876,7 +2900,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -2887,7 +2911,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -2898,7 +2922,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -2909,7 +2933,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -2920,7 +2944,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -2928,7 +2952,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -2936,7 +2960,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -2944,7 +2968,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -2952,7 +2976,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -2960,7 +2984,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -2968,7 +2992,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -2976,7 +3000,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -2984,7 +3008,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -2992,7 +3016,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3000,236 +3024,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3251,27 +3280,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3291,122 +3320,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3430,180 +3459,180 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -3621,1488 +3650,1513 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="N1:W289"/>
+  <dimension ref="N1:W294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="14:23">
       <c r="N1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="W1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="14:23">
       <c r="N2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="W2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="14:23">
       <c r="N3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="W3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="14:23">
       <c r="N4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="W4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="14:23">
       <c r="N5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="W5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="14:23">
       <c r="N6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="W6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="14:23">
       <c r="N7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="W7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="14:23">
       <c r="N8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="W8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" spans="14:23">
       <c r="N9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="W9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" spans="14:23">
       <c r="N10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="W10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="14:23">
       <c r="N11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="W11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="14:23">
       <c r="N12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="W12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="14:23">
       <c r="W13" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" spans="14:23">
       <c r="W14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15" spans="14:23">
       <c r="W15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" spans="14:23">
       <c r="W16" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="17" spans="23:23">
       <c r="W17" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" spans="23:23">
       <c r="W18" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="19" spans="23:23">
       <c r="W19" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="20" spans="23:23">
       <c r="W20" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="21" spans="23:23">
       <c r="W21" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="23:23">
       <c r="W22" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23" spans="23:23">
       <c r="W23" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="24" spans="23:23">
       <c r="W24" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="25" spans="23:23">
       <c r="W25" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="23:23">
       <c r="W26" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="23:23">
       <c r="W27" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="28" spans="23:23">
       <c r="W28" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="23:23">
       <c r="W29" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="23:23">
       <c r="W30" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" spans="23:23">
       <c r="W31" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32" spans="23:23">
       <c r="W32" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" spans="23:23">
       <c r="W33" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="34" spans="23:23">
       <c r="W34" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="35" spans="23:23">
       <c r="W35" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="36" spans="23:23">
       <c r="W36" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="37" spans="23:23">
       <c r="W37" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="38" spans="23:23">
       <c r="W38" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="39" spans="23:23">
       <c r="W39" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="40" spans="23:23">
       <c r="W40" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="41" spans="23:23">
       <c r="W41" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="42" spans="23:23">
       <c r="W42" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="43" spans="23:23">
       <c r="W43" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="44" spans="23:23">
       <c r="W44" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="45" spans="23:23">
       <c r="W45" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="46" spans="23:23">
       <c r="W46" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="47" spans="23:23">
       <c r="W47" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="48" spans="23:23">
       <c r="W48" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="49" spans="23:23">
       <c r="W49" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="50" spans="23:23">
       <c r="W50" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="51" spans="23:23">
       <c r="W51" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="52" spans="23:23">
       <c r="W52" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="53" spans="23:23">
       <c r="W53" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="54" spans="23:23">
       <c r="W54" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="55" spans="23:23">
       <c r="W55" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="56" spans="23:23">
       <c r="W56" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="57" spans="23:23">
       <c r="W57" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="58" spans="23:23">
       <c r="W58" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="59" spans="23:23">
       <c r="W59" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="60" spans="23:23">
       <c r="W60" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="61" spans="23:23">
       <c r="W61" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="62" spans="23:23">
       <c r="W62" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="63" spans="23:23">
       <c r="W63" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="64" spans="23:23">
       <c r="W64" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="65" spans="23:23">
       <c r="W65" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="66" spans="23:23">
       <c r="W66" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="67" spans="23:23">
       <c r="W67" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="68" spans="23:23">
       <c r="W68" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="69" spans="23:23">
       <c r="W69" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="70" spans="23:23">
       <c r="W70" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="71" spans="23:23">
       <c r="W71" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="72" spans="23:23">
       <c r="W72" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="73" spans="23:23">
       <c r="W73" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="74" spans="23:23">
       <c r="W74" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="75" spans="23:23">
       <c r="W75" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="76" spans="23:23">
       <c r="W76" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="77" spans="23:23">
       <c r="W77" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="78" spans="23:23">
       <c r="W78" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="79" spans="23:23">
       <c r="W79" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="80" spans="23:23">
       <c r="W80" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="81" spans="23:23">
       <c r="W81" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="82" spans="23:23">
       <c r="W82" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="83" spans="23:23">
       <c r="W83" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="84" spans="23:23">
       <c r="W84" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="85" spans="23:23">
       <c r="W85" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="86" spans="23:23">
       <c r="W86" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="87" spans="23:23">
       <c r="W87" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="88" spans="23:23">
       <c r="W88" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="89" spans="23:23">
       <c r="W89" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="90" spans="23:23">
       <c r="W90" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="91" spans="23:23">
       <c r="W91" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="92" spans="23:23">
       <c r="W92" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="93" spans="23:23">
       <c r="W93" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="94" spans="23:23">
       <c r="W94" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="95" spans="23:23">
       <c r="W95" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="96" spans="23:23">
       <c r="W96" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="97" spans="23:23">
       <c r="W97" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="98" spans="23:23">
       <c r="W98" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="99" spans="23:23">
       <c r="W99" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="100" spans="23:23">
       <c r="W100" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="101" spans="23:23">
       <c r="W101" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="102" spans="23:23">
       <c r="W102" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="103" spans="23:23">
       <c r="W103" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="104" spans="23:23">
       <c r="W104" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="105" spans="23:23">
       <c r="W105" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="106" spans="23:23">
       <c r="W106" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="107" spans="23:23">
       <c r="W107" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="108" spans="23:23">
       <c r="W108" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="109" spans="23:23">
       <c r="W109" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="110" spans="23:23">
       <c r="W110" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="111" spans="23:23">
       <c r="W111" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="112" spans="23:23">
       <c r="W112" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="113" spans="23:23">
       <c r="W113" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="114" spans="23:23">
       <c r="W114" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="115" spans="23:23">
       <c r="W115" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="116" spans="23:23">
       <c r="W116" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="117" spans="23:23">
       <c r="W117" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="118" spans="23:23">
       <c r="W118" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="119" spans="23:23">
       <c r="W119" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="120" spans="23:23">
       <c r="W120" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="121" spans="23:23">
       <c r="W121" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="122" spans="23:23">
       <c r="W122" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="123" spans="23:23">
       <c r="W123" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="124" spans="23:23">
       <c r="W124" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="125" spans="23:23">
       <c r="W125" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="126" spans="23:23">
       <c r="W126" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="127" spans="23:23">
       <c r="W127" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="128" spans="23:23">
       <c r="W128" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="129" spans="23:23">
       <c r="W129" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="130" spans="23:23">
       <c r="W130" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="131" spans="23:23">
       <c r="W131" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="132" spans="23:23">
       <c r="W132" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="133" spans="23:23">
       <c r="W133" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="134" spans="23:23">
       <c r="W134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="135" spans="23:23">
       <c r="W135" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="136" spans="23:23">
       <c r="W136" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="137" spans="23:23">
       <c r="W137" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="138" spans="23:23">
       <c r="W138" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="139" spans="23:23">
       <c r="W139" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="140" spans="23:23">
       <c r="W140" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="141" spans="23:23">
       <c r="W141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="142" spans="23:23">
       <c r="W142" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="143" spans="23:23">
       <c r="W143" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="144" spans="23:23">
       <c r="W144" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="145" spans="23:23">
       <c r="W145" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="146" spans="23:23">
       <c r="W146" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="147" spans="23:23">
       <c r="W147" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="148" spans="23:23">
       <c r="W148" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="149" spans="23:23">
       <c r="W149" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="150" spans="23:23">
       <c r="W150" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="151" spans="23:23">
       <c r="W151" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="152" spans="23:23">
       <c r="W152" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="153" spans="23:23">
       <c r="W153" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="154" spans="23:23">
       <c r="W154" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="155" spans="23:23">
       <c r="W155" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="156" spans="23:23">
       <c r="W156" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="157" spans="23:23">
       <c r="W157" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="158" spans="23:23">
       <c r="W158" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="159" spans="23:23">
       <c r="W159" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="160" spans="23:23">
       <c r="W160" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="161" spans="23:23">
       <c r="W161" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="162" spans="23:23">
       <c r="W162" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="163" spans="23:23">
       <c r="W163" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="164" spans="23:23">
       <c r="W164" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="165" spans="23:23">
       <c r="W165" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="166" spans="23:23">
       <c r="W166" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="167" spans="23:23">
       <c r="W167" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="168" spans="23:23">
       <c r="W168" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="169" spans="23:23">
       <c r="W169" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="170" spans="23:23">
       <c r="W170" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="171" spans="23:23">
       <c r="W171" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="172" spans="23:23">
       <c r="W172" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="173" spans="23:23">
       <c r="W173" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="174" spans="23:23">
       <c r="W174" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="175" spans="23:23">
       <c r="W175" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="176" spans="23:23">
       <c r="W176" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="177" spans="23:23">
       <c r="W177" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="178" spans="23:23">
       <c r="W178" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="179" spans="23:23">
       <c r="W179" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="180" spans="23:23">
       <c r="W180" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="181" spans="23:23">
       <c r="W181" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="182" spans="23:23">
       <c r="W182" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="183" spans="23:23">
       <c r="W183" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="184" spans="23:23">
       <c r="W184" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="185" spans="23:23">
       <c r="W185" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="186" spans="23:23">
       <c r="W186" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="187" spans="23:23">
       <c r="W187" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="188" spans="23:23">
       <c r="W188" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="189" spans="23:23">
       <c r="W189" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="190" spans="23:23">
       <c r="W190" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="191" spans="23:23">
       <c r="W191" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="192" spans="23:23">
       <c r="W192" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="193" spans="23:23">
       <c r="W193" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="194" spans="23:23">
       <c r="W194" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="195" spans="23:23">
       <c r="W195" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="196" spans="23:23">
       <c r="W196" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="197" spans="23:23">
       <c r="W197" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="198" spans="23:23">
       <c r="W198" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="199" spans="23:23">
       <c r="W199" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="200" spans="23:23">
       <c r="W200" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="201" spans="23:23">
       <c r="W201" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="202" spans="23:23">
       <c r="W202" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="203" spans="23:23">
       <c r="W203" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="204" spans="23:23">
       <c r="W204" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="205" spans="23:23">
       <c r="W205" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="206" spans="23:23">
       <c r="W206" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="207" spans="23:23">
       <c r="W207" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="208" spans="23:23">
       <c r="W208" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="209" spans="23:23">
       <c r="W209" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="210" spans="23:23">
       <c r="W210" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="211" spans="23:23">
       <c r="W211" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="212" spans="23:23">
       <c r="W212" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="213" spans="23:23">
       <c r="W213" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="214" spans="23:23">
       <c r="W214" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="215" spans="23:23">
       <c r="W215" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="216" spans="23:23">
       <c r="W216" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="217" spans="23:23">
       <c r="W217" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="218" spans="23:23">
       <c r="W218" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="219" spans="23:23">
       <c r="W219" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="220" spans="23:23">
       <c r="W220" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="221" spans="23:23">
       <c r="W221" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="222" spans="23:23">
       <c r="W222" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="223" spans="23:23">
       <c r="W223" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="224" spans="23:23">
       <c r="W224" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="225" spans="23:23">
       <c r="W225" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="226" spans="23:23">
       <c r="W226" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="227" spans="23:23">
       <c r="W227" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="228" spans="23:23">
       <c r="W228" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="229" spans="23:23">
       <c r="W229" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="230" spans="23:23">
       <c r="W230" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="231" spans="23:23">
       <c r="W231" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="232" spans="23:23">
       <c r="W232" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="233" spans="23:23">
       <c r="W233" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="234" spans="23:23">
       <c r="W234" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="235" spans="23:23">
       <c r="W235" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="236" spans="23:23">
       <c r="W236" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="237" spans="23:23">
       <c r="W237" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="238" spans="23:23">
       <c r="W238" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="239" spans="23:23">
       <c r="W239" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="240" spans="23:23">
       <c r="W240" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="241" spans="23:23">
       <c r="W241" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="242" spans="23:23">
       <c r="W242" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="243" spans="23:23">
       <c r="W243" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="244" spans="23:23">
       <c r="W244" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="245" spans="23:23">
       <c r="W245" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="246" spans="23:23">
       <c r="W246" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="247" spans="23:23">
       <c r="W247" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="248" spans="23:23">
       <c r="W248" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="249" spans="23:23">
       <c r="W249" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="250" spans="23:23">
       <c r="W250" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="251" spans="23:23">
       <c r="W251" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="252" spans="23:23">
       <c r="W252" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="253" spans="23:23">
       <c r="W253" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="254" spans="23:23">
       <c r="W254" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="255" spans="23:23">
       <c r="W255" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="256" spans="23:23">
       <c r="W256" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="257" spans="23:23">
       <c r="W257" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="258" spans="23:23">
       <c r="W258" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="259" spans="23:23">
       <c r="W259" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="260" spans="23:23">
       <c r="W260" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="261" spans="23:23">
       <c r="W261" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="262" spans="23:23">
       <c r="W262" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="263" spans="23:23">
       <c r="W263" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="264" spans="23:23">
       <c r="W264" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="265" spans="23:23">
       <c r="W265" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="266" spans="23:23">
       <c r="W266" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="267" spans="23:23">
       <c r="W267" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="268" spans="23:23">
       <c r="W268" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="269" spans="23:23">
       <c r="W269" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="270" spans="23:23">
       <c r="W270" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="271" spans="23:23">
       <c r="W271" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="272" spans="23:23">
       <c r="W272" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="273" spans="23:23">
       <c r="W273" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="274" spans="23:23">
       <c r="W274" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="275" spans="23:23">
       <c r="W275" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="276" spans="23:23">
       <c r="W276" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="277" spans="23:23">
       <c r="W277" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="278" spans="23:23">
       <c r="W278" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="279" spans="23:23">
       <c r="W279" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="280" spans="23:23">
       <c r="W280" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="281" spans="23:23">
       <c r="W281" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="282" spans="23:23">
       <c r="W282" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="283" spans="23:23">
       <c r="W283" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="284" spans="23:23">
       <c r="W284" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="285" spans="23:23">
       <c r="W285" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="286" spans="23:23">
       <c r="W286" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="287" spans="23:23">
       <c r="W287" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="288" spans="23:23">
       <c r="W288" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="289" spans="23:23">
       <c r="W289" t="s">
-        <v>606</v>
+        <v>608</v>
+      </c>
+    </row>
+    <row r="290" spans="23:23">
+      <c r="W290" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="291" spans="23:23">
+      <c r="W291" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="292" spans="23:23">
+      <c r="W292" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="293" spans="23:23">
+      <c r="W293" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="294" spans="23:23">
+      <c r="W294" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000036/metadata_template_ERC000036.xlsx
+++ b/templates/ERC000036/metadata_template_ERC000036.xlsx
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$U$1:$U$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
-    <definedName name="investigationtype">'cv_sample'!$L$1:$L$12</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$V$1:$V$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="investigationtype">'cv_sample'!$M$1:$M$12</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="628">
   <si>
     <t>alias</t>
   </si>
@@ -448,6 +448,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -538,6 +541,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -838,6 +844,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -1189,9 +1201,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1210,6 +1219,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1411,6 +1423,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1420,9 +1435,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1462,7 +1474,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1531,6 +1543,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1606,6 +1621,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1627,6 +1645,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1672,6 +1693,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1684,6 +1708,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1693,9 +1720,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1720,6 +1744,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1780,10 +1807,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -2415,10 +2442,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2459,10 +2486,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2489,7 +2516,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2506,7 +2533,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2523,7 +2550,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2540,7 +2567,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2557,7 +2584,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2574,7 +2601,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2591,7 +2618,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2608,7 +2635,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2625,7 +2652,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2642,7 +2669,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2656,7 +2683,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2670,7 +2697,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2684,7 +2711,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2698,7 +2725,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2712,7 +2739,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2726,7 +2753,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2740,7 +2767,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2754,7 +2781,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2764,8 +2791,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2776,7 +2806,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2787,7 +2817,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -2798,7 +2828,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -2809,7 +2839,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -2820,7 +2850,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -2831,7 +2861,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -2842,7 +2872,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -2853,7 +2883,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -2864,7 +2894,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -2875,7 +2905,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -2886,7 +2916,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -2897,7 +2927,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -2908,7 +2938,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -2916,7 +2946,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -2924,7 +2954,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -2932,7 +2962,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -2940,7 +2970,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -2948,7 +2978,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -2956,7 +2986,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -2964,7 +2994,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -2972,7 +3002,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -2980,7 +3010,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -2988,236 +3018,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3239,27 +3274,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3279,122 +3314,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3404,13 +3439,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3418,176 +3453,182 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" ht="150" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="Z1" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="V2" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="W2" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="X2" s="2" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" ht="150" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>610</v>
-      </c>
       <c r="Y2" s="2" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>618</v>
+        <v>625</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>627</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M101">
       <formula1>investigationtype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V3:V101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
   </dataValidations>
@@ -3597,1488 +3638,1513 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="L1:U289"/>
+  <dimension ref="M1:V294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="12:21">
-      <c r="L1" t="s">
-        <v>284</v>
-      </c>
-      <c r="U1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="2" spans="12:21">
-      <c r="L2" t="s">
-        <v>285</v>
-      </c>
-      <c r="U2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="3" spans="12:21">
-      <c r="L3" t="s">
-        <v>286</v>
-      </c>
-      <c r="U3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="4" spans="12:21">
-      <c r="L4" t="s">
-        <v>287</v>
-      </c>
-      <c r="U4" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="5" spans="12:21">
-      <c r="L5" t="s">
+    <row r="1" spans="13:22">
+      <c r="M1" t="s">
         <v>288</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V1" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="6" spans="12:21">
-      <c r="L6" t="s">
+    <row r="2" spans="13:22">
+      <c r="M2" t="s">
         <v>289</v>
       </c>
-      <c r="U6" t="s">
+      <c r="V2" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="7" spans="12:21">
-      <c r="L7" t="s">
+    <row r="3" spans="13:22">
+      <c r="M3" t="s">
         <v>290</v>
       </c>
-      <c r="U7" t="s">
+      <c r="V3" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="8" spans="12:21">
-      <c r="L8" t="s">
+    <row r="4" spans="13:22">
+      <c r="M4" t="s">
         <v>291</v>
       </c>
-      <c r="U8" t="s">
+      <c r="V4" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="9" spans="12:21">
-      <c r="L9" t="s">
+    <row r="5" spans="13:22">
+      <c r="M5" t="s">
         <v>292</v>
       </c>
-      <c r="U9" t="s">
+      <c r="V5" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="10" spans="12:21">
-      <c r="L10" t="s">
+    <row r="6" spans="13:22">
+      <c r="M6" t="s">
         <v>293</v>
       </c>
-      <c r="U10" t="s">
+      <c r="V6" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="11" spans="12:21">
-      <c r="L11" t="s">
+    <row r="7" spans="13:22">
+      <c r="M7" t="s">
         <v>294</v>
       </c>
-      <c r="U11" t="s">
+      <c r="V7" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="12" spans="12:21">
-      <c r="L12" t="s">
+    <row r="8" spans="13:22">
+      <c r="M8" t="s">
         <v>295</v>
       </c>
-      <c r="U12" t="s">
+      <c r="V8" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="13" spans="12:21">
-      <c r="U13" t="s">
+    <row r="9" spans="13:22">
+      <c r="M9" t="s">
+        <v>296</v>
+      </c>
+      <c r="V9" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="14" spans="12:21">
-      <c r="U14" t="s">
+    <row r="10" spans="13:22">
+      <c r="M10" t="s">
+        <v>297</v>
+      </c>
+      <c r="V10" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="15" spans="12:21">
-      <c r="U15" t="s">
+    <row r="11" spans="13:22">
+      <c r="M11" t="s">
+        <v>298</v>
+      </c>
+      <c r="V11" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="16" spans="12:21">
-      <c r="U16" t="s">
+    <row r="12" spans="13:22">
+      <c r="M12" t="s">
+        <v>299</v>
+      </c>
+      <c r="V12" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="17" spans="21:21">
-      <c r="U17" t="s">
+    <row r="13" spans="13:22">
+      <c r="V13" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="18" spans="21:21">
-      <c r="U18" t="s">
+    <row r="14" spans="13:22">
+      <c r="V14" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="19" spans="21:21">
-      <c r="U19" t="s">
+    <row r="15" spans="13:22">
+      <c r="V15" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="20" spans="21:21">
-      <c r="U20" t="s">
+    <row r="16" spans="13:22">
+      <c r="V16" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="21" spans="21:21">
-      <c r="U21" t="s">
+    <row r="17" spans="22:22">
+      <c r="V17" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="22" spans="21:21">
-      <c r="U22" t="s">
+    <row r="18" spans="22:22">
+      <c r="V18" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="23" spans="21:21">
-      <c r="U23" t="s">
+    <row r="19" spans="22:22">
+      <c r="V19" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="24" spans="21:21">
-      <c r="U24" t="s">
+    <row r="20" spans="22:22">
+      <c r="V20" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="25" spans="21:21">
-      <c r="U25" t="s">
+    <row r="21" spans="22:22">
+      <c r="V21" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="26" spans="21:21">
-      <c r="U26" t="s">
+    <row r="22" spans="22:22">
+      <c r="V22" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="27" spans="21:21">
-      <c r="U27" t="s">
+    <row r="23" spans="22:22">
+      <c r="V23" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="28" spans="21:21">
-      <c r="U28" t="s">
+    <row r="24" spans="22:22">
+      <c r="V24" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="29" spans="21:21">
-      <c r="U29" t="s">
+    <row r="25" spans="22:22">
+      <c r="V25" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="30" spans="21:21">
-      <c r="U30" t="s">
+    <row r="26" spans="22:22">
+      <c r="V26" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="31" spans="21:21">
-      <c r="U31" t="s">
+    <row r="27" spans="22:22">
+      <c r="V27" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="32" spans="21:21">
-      <c r="U32" t="s">
+    <row r="28" spans="22:22">
+      <c r="V28" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="33" spans="21:21">
-      <c r="U33" t="s">
+    <row r="29" spans="22:22">
+      <c r="V29" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="34" spans="21:21">
-      <c r="U34" t="s">
+    <row r="30" spans="22:22">
+      <c r="V30" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="35" spans="21:21">
-      <c r="U35" t="s">
+    <row r="31" spans="22:22">
+      <c r="V31" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="36" spans="21:21">
-      <c r="U36" t="s">
+    <row r="32" spans="22:22">
+      <c r="V32" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="37" spans="21:21">
-      <c r="U37" t="s">
+    <row r="33" spans="22:22">
+      <c r="V33" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="38" spans="21:21">
-      <c r="U38" t="s">
+    <row r="34" spans="22:22">
+      <c r="V34" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="39" spans="21:21">
-      <c r="U39" t="s">
+    <row r="35" spans="22:22">
+      <c r="V35" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="40" spans="21:21">
-      <c r="U40" t="s">
+    <row r="36" spans="22:22">
+      <c r="V36" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="41" spans="21:21">
-      <c r="U41" t="s">
+    <row r="37" spans="22:22">
+      <c r="V37" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="42" spans="21:21">
-      <c r="U42" t="s">
+    <row r="38" spans="22:22">
+      <c r="V38" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="43" spans="21:21">
-      <c r="U43" t="s">
+    <row r="39" spans="22:22">
+      <c r="V39" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="44" spans="21:21">
-      <c r="U44" t="s">
+    <row r="40" spans="22:22">
+      <c r="V40" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="45" spans="21:21">
-      <c r="U45" t="s">
+    <row r="41" spans="22:22">
+      <c r="V41" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="46" spans="21:21">
-      <c r="U46" t="s">
+    <row r="42" spans="22:22">
+      <c r="V42" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="47" spans="21:21">
-      <c r="U47" t="s">
+    <row r="43" spans="22:22">
+      <c r="V43" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="48" spans="21:21">
-      <c r="U48" t="s">
+    <row r="44" spans="22:22">
+      <c r="V44" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="21:21">
-      <c r="U49" t="s">
+    <row r="45" spans="22:22">
+      <c r="V45" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="50" spans="21:21">
-      <c r="U50" t="s">
+    <row r="46" spans="22:22">
+      <c r="V46" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="51" spans="21:21">
-      <c r="U51" t="s">
+    <row r="47" spans="22:22">
+      <c r="V47" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="52" spans="21:21">
-      <c r="U52" t="s">
+    <row r="48" spans="22:22">
+      <c r="V48" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="53" spans="21:21">
-      <c r="U53" t="s">
+    <row r="49" spans="22:22">
+      <c r="V49" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="54" spans="21:21">
-      <c r="U54" t="s">
+    <row r="50" spans="22:22">
+      <c r="V50" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="55" spans="21:21">
-      <c r="U55" t="s">
+    <row r="51" spans="22:22">
+      <c r="V51" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="56" spans="21:21">
-      <c r="U56" t="s">
+    <row r="52" spans="22:22">
+      <c r="V52" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="57" spans="21:21">
-      <c r="U57" t="s">
+    <row r="53" spans="22:22">
+      <c r="V53" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="58" spans="21:21">
-      <c r="U58" t="s">
+    <row r="54" spans="22:22">
+      <c r="V54" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="59" spans="21:21">
-      <c r="U59" t="s">
+    <row r="55" spans="22:22">
+      <c r="V55" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="60" spans="21:21">
-      <c r="U60" t="s">
+    <row r="56" spans="22:22">
+      <c r="V56" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="61" spans="21:21">
-      <c r="U61" t="s">
+    <row r="57" spans="22:22">
+      <c r="V57" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="62" spans="21:21">
-      <c r="U62" t="s">
+    <row r="58" spans="22:22">
+      <c r="V58" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="63" spans="21:21">
-      <c r="U63" t="s">
+    <row r="59" spans="22:22">
+      <c r="V59" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="64" spans="21:21">
-      <c r="U64" t="s">
+    <row r="60" spans="22:22">
+      <c r="V60" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="65" spans="21:21">
-      <c r="U65" t="s">
+    <row r="61" spans="22:22">
+      <c r="V61" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="66" spans="21:21">
-      <c r="U66" t="s">
+    <row r="62" spans="22:22">
+      <c r="V62" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="67" spans="21:21">
-      <c r="U67" t="s">
+    <row r="63" spans="22:22">
+      <c r="V63" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="68" spans="21:21">
-      <c r="U68" t="s">
+    <row r="64" spans="22:22">
+      <c r="V64" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="69" spans="21:21">
-      <c r="U69" t="s">
+    <row r="65" spans="22:22">
+      <c r="V65" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="70" spans="21:21">
-      <c r="U70" t="s">
+    <row r="66" spans="22:22">
+      <c r="V66" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="71" spans="21:21">
-      <c r="U71" t="s">
+    <row r="67" spans="22:22">
+      <c r="V67" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="72" spans="21:21">
-      <c r="U72" t="s">
+    <row r="68" spans="22:22">
+      <c r="V68" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="73" spans="21:21">
-      <c r="U73" t="s">
+    <row r="69" spans="22:22">
+      <c r="V69" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="74" spans="21:21">
-      <c r="U74" t="s">
+    <row r="70" spans="22:22">
+      <c r="V70" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="75" spans="21:21">
-      <c r="U75" t="s">
+    <row r="71" spans="22:22">
+      <c r="V71" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="76" spans="21:21">
-      <c r="U76" t="s">
+    <row r="72" spans="22:22">
+      <c r="V72" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="77" spans="21:21">
-      <c r="U77" t="s">
+    <row r="73" spans="22:22">
+      <c r="V73" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="78" spans="21:21">
-      <c r="U78" t="s">
+    <row r="74" spans="22:22">
+      <c r="V74" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="79" spans="21:21">
-      <c r="U79" t="s">
+    <row r="75" spans="22:22">
+      <c r="V75" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="80" spans="21:21">
-      <c r="U80" t="s">
+    <row r="76" spans="22:22">
+      <c r="V76" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="81" spans="21:21">
-      <c r="U81" t="s">
+    <row r="77" spans="22:22">
+      <c r="V77" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="82" spans="21:21">
-      <c r="U82" t="s">
+    <row r="78" spans="22:22">
+      <c r="V78" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="83" spans="21:21">
-      <c r="U83" t="s">
+    <row r="79" spans="22:22">
+      <c r="V79" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="84" spans="21:21">
-      <c r="U84" t="s">
+    <row r="80" spans="22:22">
+      <c r="V80" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="85" spans="21:21">
-      <c r="U85" t="s">
+    <row r="81" spans="22:22">
+      <c r="V81" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="86" spans="21:21">
-      <c r="U86" t="s">
+    <row r="82" spans="22:22">
+      <c r="V82" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="87" spans="21:21">
-      <c r="U87" t="s">
+    <row r="83" spans="22:22">
+      <c r="V83" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="88" spans="21:21">
-      <c r="U88" t="s">
+    <row r="84" spans="22:22">
+      <c r="V84" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="89" spans="21:21">
-      <c r="U89" t="s">
+    <row r="85" spans="22:22">
+      <c r="V85" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="90" spans="21:21">
-      <c r="U90" t="s">
+    <row r="86" spans="22:22">
+      <c r="V86" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="91" spans="21:21">
-      <c r="U91" t="s">
+    <row r="87" spans="22:22">
+      <c r="V87" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="92" spans="21:21">
-      <c r="U92" t="s">
+    <row r="88" spans="22:22">
+      <c r="V88" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="93" spans="21:21">
-      <c r="U93" t="s">
+    <row r="89" spans="22:22">
+      <c r="V89" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="94" spans="21:21">
-      <c r="U94" t="s">
+    <row r="90" spans="22:22">
+      <c r="V90" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="95" spans="21:21">
-      <c r="U95" t="s">
+    <row r="91" spans="22:22">
+      <c r="V91" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="96" spans="21:21">
-      <c r="U96" t="s">
+    <row r="92" spans="22:22">
+      <c r="V92" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="97" spans="21:21">
-      <c r="U97" t="s">
+    <row r="93" spans="22:22">
+      <c r="V93" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="98" spans="21:21">
-      <c r="U98" t="s">
+    <row r="94" spans="22:22">
+      <c r="V94" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="99" spans="21:21">
-      <c r="U99" t="s">
+    <row r="95" spans="22:22">
+      <c r="V95" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="100" spans="21:21">
-      <c r="U100" t="s">
+    <row r="96" spans="22:22">
+      <c r="V96" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="101" spans="21:21">
-      <c r="U101" t="s">
+    <row r="97" spans="22:22">
+      <c r="V97" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="102" spans="21:21">
-      <c r="U102" t="s">
+    <row r="98" spans="22:22">
+      <c r="V98" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="103" spans="21:21">
-      <c r="U103" t="s">
+    <row r="99" spans="22:22">
+      <c r="V99" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="104" spans="21:21">
-      <c r="U104" t="s">
+    <row r="100" spans="22:22">
+      <c r="V100" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="105" spans="21:21">
-      <c r="U105" t="s">
+    <row r="101" spans="22:22">
+      <c r="V101" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="106" spans="21:21">
-      <c r="U106" t="s">
+    <row r="102" spans="22:22">
+      <c r="V102" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="107" spans="21:21">
-      <c r="U107" t="s">
+    <row r="103" spans="22:22">
+      <c r="V103" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="108" spans="21:21">
-      <c r="U108" t="s">
+    <row r="104" spans="22:22">
+      <c r="V104" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="109" spans="21:21">
-      <c r="U109" t="s">
+    <row r="105" spans="22:22">
+      <c r="V105" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="110" spans="21:21">
-      <c r="U110" t="s">
+    <row r="106" spans="22:22">
+      <c r="V106" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="111" spans="21:21">
-      <c r="U111" t="s">
+    <row r="107" spans="22:22">
+      <c r="V107" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="112" spans="21:21">
-      <c r="U112" t="s">
+    <row r="108" spans="22:22">
+      <c r="V108" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="113" spans="21:21">
-      <c r="U113" t="s">
+    <row r="109" spans="22:22">
+      <c r="V109" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="114" spans="21:21">
-      <c r="U114" t="s">
+    <row r="110" spans="22:22">
+      <c r="V110" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="115" spans="21:21">
-      <c r="U115" t="s">
+    <row r="111" spans="22:22">
+      <c r="V111" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="116" spans="21:21">
-      <c r="U116" t="s">
+    <row r="112" spans="22:22">
+      <c r="V112" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="117" spans="21:21">
-      <c r="U117" t="s">
+    <row r="113" spans="22:22">
+      <c r="V113" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="118" spans="21:21">
-      <c r="U118" t="s">
+    <row r="114" spans="22:22">
+      <c r="V114" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="119" spans="21:21">
-      <c r="U119" t="s">
+    <row r="115" spans="22:22">
+      <c r="V115" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="120" spans="21:21">
-      <c r="U120" t="s">
+    <row r="116" spans="22:22">
+      <c r="V116" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="121" spans="21:21">
-      <c r="U121" t="s">
+    <row r="117" spans="22:22">
+      <c r="V117" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="122" spans="21:21">
-      <c r="U122" t="s">
+    <row r="118" spans="22:22">
+      <c r="V118" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="123" spans="21:21">
-      <c r="U123" t="s">
+    <row r="119" spans="22:22">
+      <c r="V119" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="124" spans="21:21">
-      <c r="U124" t="s">
+    <row r="120" spans="22:22">
+      <c r="V120" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="125" spans="21:21">
-      <c r="U125" t="s">
+    <row r="121" spans="22:22">
+      <c r="V121" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="126" spans="21:21">
-      <c r="U126" t="s">
+    <row r="122" spans="22:22">
+      <c r="V122" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="127" spans="21:21">
-      <c r="U127" t="s">
+    <row r="123" spans="22:22">
+      <c r="V123" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="128" spans="21:21">
-      <c r="U128" t="s">
+    <row r="124" spans="22:22">
+      <c r="V124" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="129" spans="21:21">
-      <c r="U129" t="s">
+    <row r="125" spans="22:22">
+      <c r="V125" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="130" spans="21:21">
-      <c r="U130" t="s">
+    <row r="126" spans="22:22">
+      <c r="V126" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="131" spans="21:21">
-      <c r="U131" t="s">
+    <row r="127" spans="22:22">
+      <c r="V127" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="132" spans="21:21">
-      <c r="U132" t="s">
+    <row r="128" spans="22:22">
+      <c r="V128" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="133" spans="21:21">
-      <c r="U133" t="s">
+    <row r="129" spans="22:22">
+      <c r="V129" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="134" spans="21:21">
-      <c r="U134" t="s">
+    <row r="130" spans="22:22">
+      <c r="V130" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="135" spans="21:21">
-      <c r="U135" t="s">
+    <row r="131" spans="22:22">
+      <c r="V131" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="136" spans="21:21">
-      <c r="U136" t="s">
+    <row r="132" spans="22:22">
+      <c r="V132" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="137" spans="21:21">
-      <c r="U137" t="s">
+    <row r="133" spans="22:22">
+      <c r="V133" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="138" spans="21:21">
-      <c r="U138" t="s">
+    <row r="134" spans="22:22">
+      <c r="V134" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="139" spans="21:21">
-      <c r="U139" t="s">
+    <row r="135" spans="22:22">
+      <c r="V135" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="140" spans="21:21">
-      <c r="U140" t="s">
+    <row r="136" spans="22:22">
+      <c r="V136" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="141" spans="21:21">
-      <c r="U141" t="s">
+    <row r="137" spans="22:22">
+      <c r="V137" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="142" spans="21:21">
-      <c r="U142" t="s">
+    <row r="138" spans="22:22">
+      <c r="V138" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="143" spans="21:21">
-      <c r="U143" t="s">
+    <row r="139" spans="22:22">
+      <c r="V139" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="144" spans="21:21">
-      <c r="U144" t="s">
+    <row r="140" spans="22:22">
+      <c r="V140" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="145" spans="21:21">
-      <c r="U145" t="s">
+    <row r="141" spans="22:22">
+      <c r="V141" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="146" spans="21:21">
-      <c r="U146" t="s">
+    <row r="142" spans="22:22">
+      <c r="V142" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="147" spans="21:21">
-      <c r="U147" t="s">
+    <row r="143" spans="22:22">
+      <c r="V143" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="148" spans="21:21">
-      <c r="U148" t="s">
+    <row r="144" spans="22:22">
+      <c r="V144" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="149" spans="21:21">
-      <c r="U149" t="s">
+    <row r="145" spans="22:22">
+      <c r="V145" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="150" spans="21:21">
-      <c r="U150" t="s">
+    <row r="146" spans="22:22">
+      <c r="V146" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="151" spans="21:21">
-      <c r="U151" t="s">
+    <row r="147" spans="22:22">
+      <c r="V147" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="152" spans="21:21">
-      <c r="U152" t="s">
+    <row r="148" spans="22:22">
+      <c r="V148" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="153" spans="21:21">
-      <c r="U153" t="s">
+    <row r="149" spans="22:22">
+      <c r="V149" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="154" spans="21:21">
-      <c r="U154" t="s">
+    <row r="150" spans="22:22">
+      <c r="V150" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="155" spans="21:21">
-      <c r="U155" t="s">
+    <row r="151" spans="22:22">
+      <c r="V151" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="156" spans="21:21">
-      <c r="U156" t="s">
+    <row r="152" spans="22:22">
+      <c r="V152" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="157" spans="21:21">
-      <c r="U157" t="s">
+    <row r="153" spans="22:22">
+      <c r="V153" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="158" spans="21:21">
-      <c r="U158" t="s">
+    <row r="154" spans="22:22">
+      <c r="V154" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="159" spans="21:21">
-      <c r="U159" t="s">
+    <row r="155" spans="22:22">
+      <c r="V155" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="160" spans="21:21">
-      <c r="U160" t="s">
+    <row r="156" spans="22:22">
+      <c r="V156" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="161" spans="21:21">
-      <c r="U161" t="s">
+    <row r="157" spans="22:22">
+      <c r="V157" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="162" spans="21:21">
-      <c r="U162" t="s">
+    <row r="158" spans="22:22">
+      <c r="V158" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="163" spans="21:21">
-      <c r="U163" t="s">
+    <row r="159" spans="22:22">
+      <c r="V159" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="164" spans="21:21">
-      <c r="U164" t="s">
+    <row r="160" spans="22:22">
+      <c r="V160" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="165" spans="21:21">
-      <c r="U165" t="s">
+    <row r="161" spans="22:22">
+      <c r="V161" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="166" spans="21:21">
-      <c r="U166" t="s">
+    <row r="162" spans="22:22">
+      <c r="V162" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="167" spans="21:21">
-      <c r="U167" t="s">
+    <row r="163" spans="22:22">
+      <c r="V163" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="168" spans="21:21">
-      <c r="U168" t="s">
+    <row r="164" spans="22:22">
+      <c r="V164" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="169" spans="21:21">
-      <c r="U169" t="s">
+    <row r="165" spans="22:22">
+      <c r="V165" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="170" spans="21:21">
-      <c r="U170" t="s">
+    <row r="166" spans="22:22">
+      <c r="V166" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="171" spans="21:21">
-      <c r="U171" t="s">
+    <row r="167" spans="22:22">
+      <c r="V167" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="172" spans="21:21">
-      <c r="U172" t="s">
+    <row r="168" spans="22:22">
+      <c r="V168" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="173" spans="21:21">
-      <c r="U173" t="s">
+    <row r="169" spans="22:22">
+      <c r="V169" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="174" spans="21:21">
-      <c r="U174" t="s">
+    <row r="170" spans="22:22">
+      <c r="V170" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="175" spans="21:21">
-      <c r="U175" t="s">
+    <row r="171" spans="22:22">
+      <c r="V171" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="176" spans="21:21">
-      <c r="U176" t="s">
+    <row r="172" spans="22:22">
+      <c r="V172" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="177" spans="21:21">
-      <c r="U177" t="s">
+    <row r="173" spans="22:22">
+      <c r="V173" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="178" spans="21:21">
-      <c r="U178" t="s">
+    <row r="174" spans="22:22">
+      <c r="V174" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="179" spans="21:21">
-      <c r="U179" t="s">
+    <row r="175" spans="22:22">
+      <c r="V175" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="180" spans="21:21">
-      <c r="U180" t="s">
+    <row r="176" spans="22:22">
+      <c r="V176" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="181" spans="21:21">
-      <c r="U181" t="s">
+    <row r="177" spans="22:22">
+      <c r="V177" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="182" spans="21:21">
-      <c r="U182" t="s">
+    <row r="178" spans="22:22">
+      <c r="V178" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="183" spans="21:21">
-      <c r="U183" t="s">
+    <row r="179" spans="22:22">
+      <c r="V179" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="184" spans="21:21">
-      <c r="U184" t="s">
+    <row r="180" spans="22:22">
+      <c r="V180" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="185" spans="21:21">
-      <c r="U185" t="s">
+    <row r="181" spans="22:22">
+      <c r="V181" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="186" spans="21:21">
-      <c r="U186" t="s">
+    <row r="182" spans="22:22">
+      <c r="V182" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="187" spans="21:21">
-      <c r="U187" t="s">
+    <row r="183" spans="22:22">
+      <c r="V183" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="188" spans="21:21">
-      <c r="U188" t="s">
+    <row r="184" spans="22:22">
+      <c r="V184" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="189" spans="21:21">
-      <c r="U189" t="s">
+    <row r="185" spans="22:22">
+      <c r="V185" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="190" spans="21:21">
-      <c r="U190" t="s">
+    <row r="186" spans="22:22">
+      <c r="V186" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="191" spans="21:21">
-      <c r="U191" t="s">
+    <row r="187" spans="22:22">
+      <c r="V187" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="192" spans="21:21">
-      <c r="U192" t="s">
+    <row r="188" spans="22:22">
+      <c r="V188" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="193" spans="21:21">
-      <c r="U193" t="s">
+    <row r="189" spans="22:22">
+      <c r="V189" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="194" spans="21:21">
-      <c r="U194" t="s">
+    <row r="190" spans="22:22">
+      <c r="V190" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="195" spans="21:21">
-      <c r="U195" t="s">
+    <row r="191" spans="22:22">
+      <c r="V191" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="196" spans="21:21">
-      <c r="U196" t="s">
+    <row r="192" spans="22:22">
+      <c r="V192" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="197" spans="21:21">
-      <c r="U197" t="s">
+    <row r="193" spans="22:22">
+      <c r="V193" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="198" spans="21:21">
-      <c r="U198" t="s">
+    <row r="194" spans="22:22">
+      <c r="V194" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="199" spans="21:21">
-      <c r="U199" t="s">
+    <row r="195" spans="22:22">
+      <c r="V195" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="200" spans="21:21">
-      <c r="U200" t="s">
+    <row r="196" spans="22:22">
+      <c r="V196" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="201" spans="21:21">
-      <c r="U201" t="s">
+    <row r="197" spans="22:22">
+      <c r="V197" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="202" spans="21:21">
-      <c r="U202" t="s">
+    <row r="198" spans="22:22">
+      <c r="V198" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="203" spans="21:21">
-      <c r="U203" t="s">
+    <row r="199" spans="22:22">
+      <c r="V199" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="204" spans="21:21">
-      <c r="U204" t="s">
+    <row r="200" spans="22:22">
+      <c r="V200" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="205" spans="21:21">
-      <c r="U205" t="s">
+    <row r="201" spans="22:22">
+      <c r="V201" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="206" spans="21:21">
-      <c r="U206" t="s">
+    <row r="202" spans="22:22">
+      <c r="V202" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="207" spans="21:21">
-      <c r="U207" t="s">
+    <row r="203" spans="22:22">
+      <c r="V203" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="208" spans="21:21">
-      <c r="U208" t="s">
+    <row r="204" spans="22:22">
+      <c r="V204" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="209" spans="21:21">
-      <c r="U209" t="s">
+    <row r="205" spans="22:22">
+      <c r="V205" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="210" spans="21:21">
-      <c r="U210" t="s">
+    <row r="206" spans="22:22">
+      <c r="V206" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="211" spans="21:21">
-      <c r="U211" t="s">
+    <row r="207" spans="22:22">
+      <c r="V207" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="212" spans="21:21">
-      <c r="U212" t="s">
+    <row r="208" spans="22:22">
+      <c r="V208" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="213" spans="21:21">
-      <c r="U213" t="s">
+    <row r="209" spans="22:22">
+      <c r="V209" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="214" spans="21:21">
-      <c r="U214" t="s">
+    <row r="210" spans="22:22">
+      <c r="V210" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="215" spans="21:21">
-      <c r="U215" t="s">
+    <row r="211" spans="22:22">
+      <c r="V211" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="216" spans="21:21">
-      <c r="U216" t="s">
+    <row r="212" spans="22:22">
+      <c r="V212" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="217" spans="21:21">
-      <c r="U217" t="s">
+    <row r="213" spans="22:22">
+      <c r="V213" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="218" spans="21:21">
-      <c r="U218" t="s">
+    <row r="214" spans="22:22">
+      <c r="V214" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="219" spans="21:21">
-      <c r="U219" t="s">
+    <row r="215" spans="22:22">
+      <c r="V215" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="220" spans="21:21">
-      <c r="U220" t="s">
+    <row r="216" spans="22:22">
+      <c r="V216" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="221" spans="21:21">
-      <c r="U221" t="s">
+    <row r="217" spans="22:22">
+      <c r="V217" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="222" spans="21:21">
-      <c r="U222" t="s">
+    <row r="218" spans="22:22">
+      <c r="V218" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="223" spans="21:21">
-      <c r="U223" t="s">
+    <row r="219" spans="22:22">
+      <c r="V219" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="224" spans="21:21">
-      <c r="U224" t="s">
+    <row r="220" spans="22:22">
+      <c r="V220" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="225" spans="21:21">
-      <c r="U225" t="s">
+    <row r="221" spans="22:22">
+      <c r="V221" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="226" spans="21:21">
-      <c r="U226" t="s">
+    <row r="222" spans="22:22">
+      <c r="V222" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="227" spans="21:21">
-      <c r="U227" t="s">
+    <row r="223" spans="22:22">
+      <c r="V223" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="228" spans="21:21">
-      <c r="U228" t="s">
+    <row r="224" spans="22:22">
+      <c r="V224" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="229" spans="21:21">
-      <c r="U229" t="s">
+    <row r="225" spans="22:22">
+      <c r="V225" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="230" spans="21:21">
-      <c r="U230" t="s">
+    <row r="226" spans="22:22">
+      <c r="V226" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="231" spans="21:21">
-      <c r="U231" t="s">
+    <row r="227" spans="22:22">
+      <c r="V227" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="232" spans="21:21">
-      <c r="U232" t="s">
+    <row r="228" spans="22:22">
+      <c r="V228" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="233" spans="21:21">
-      <c r="U233" t="s">
+    <row r="229" spans="22:22">
+      <c r="V229" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="234" spans="21:21">
-      <c r="U234" t="s">
+    <row r="230" spans="22:22">
+      <c r="V230" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="235" spans="21:21">
-      <c r="U235" t="s">
+    <row r="231" spans="22:22">
+      <c r="V231" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="236" spans="21:21">
-      <c r="U236" t="s">
+    <row r="232" spans="22:22">
+      <c r="V232" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="237" spans="21:21">
-      <c r="U237" t="s">
+    <row r="233" spans="22:22">
+      <c r="V233" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="238" spans="21:21">
-      <c r="U238" t="s">
+    <row r="234" spans="22:22">
+      <c r="V234" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="239" spans="21:21">
-      <c r="U239" t="s">
+    <row r="235" spans="22:22">
+      <c r="V235" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="240" spans="21:21">
-      <c r="U240" t="s">
+    <row r="236" spans="22:22">
+      <c r="V236" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="241" spans="21:21">
-      <c r="U241" t="s">
+    <row r="237" spans="22:22">
+      <c r="V237" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="242" spans="21:21">
-      <c r="U242" t="s">
+    <row r="238" spans="22:22">
+      <c r="V238" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="243" spans="21:21">
-      <c r="U243" t="s">
+    <row r="239" spans="22:22">
+      <c r="V239" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="244" spans="21:21">
-      <c r="U244" t="s">
+    <row r="240" spans="22:22">
+      <c r="V240" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="245" spans="21:21">
-      <c r="U245" t="s">
+    <row r="241" spans="22:22">
+      <c r="V241" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="246" spans="21:21">
-      <c r="U246" t="s">
+    <row r="242" spans="22:22">
+      <c r="V242" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="247" spans="21:21">
-      <c r="U247" t="s">
+    <row r="243" spans="22:22">
+      <c r="V243" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="248" spans="21:21">
-      <c r="U248" t="s">
+    <row r="244" spans="22:22">
+      <c r="V244" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="249" spans="21:21">
-      <c r="U249" t="s">
+    <row r="245" spans="22:22">
+      <c r="V245" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="250" spans="21:21">
-      <c r="U250" t="s">
+    <row r="246" spans="22:22">
+      <c r="V246" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="251" spans="21:21">
-      <c r="U251" t="s">
+    <row r="247" spans="22:22">
+      <c r="V247" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="252" spans="21:21">
-      <c r="U252" t="s">
+    <row r="248" spans="22:22">
+      <c r="V248" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="253" spans="21:21">
-      <c r="U253" t="s">
+    <row r="249" spans="22:22">
+      <c r="V249" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="254" spans="21:21">
-      <c r="U254" t="s">
+    <row r="250" spans="22:22">
+      <c r="V250" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="255" spans="21:21">
-      <c r="U255" t="s">
+    <row r="251" spans="22:22">
+      <c r="V251" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="256" spans="21:21">
-      <c r="U256" t="s">
+    <row r="252" spans="22:22">
+      <c r="V252" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="257" spans="21:21">
-      <c r="U257" t="s">
+    <row r="253" spans="22:22">
+      <c r="V253" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="258" spans="21:21">
-      <c r="U258" t="s">
+    <row r="254" spans="22:22">
+      <c r="V254" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="259" spans="21:21">
-      <c r="U259" t="s">
+    <row r="255" spans="22:22">
+      <c r="V255" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="260" spans="21:21">
-      <c r="U260" t="s">
+    <row r="256" spans="22:22">
+      <c r="V256" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="261" spans="21:21">
-      <c r="U261" t="s">
+    <row r="257" spans="22:22">
+      <c r="V257" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="262" spans="21:21">
-      <c r="U262" t="s">
+    <row r="258" spans="22:22">
+      <c r="V258" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="263" spans="21:21">
-      <c r="U263" t="s">
+    <row r="259" spans="22:22">
+      <c r="V259" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="264" spans="21:21">
-      <c r="U264" t="s">
+    <row r="260" spans="22:22">
+      <c r="V260" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="265" spans="21:21">
-      <c r="U265" t="s">
+    <row r="261" spans="22:22">
+      <c r="V261" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="266" spans="21:21">
-      <c r="U266" t="s">
+    <row r="262" spans="22:22">
+      <c r="V262" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="267" spans="21:21">
-      <c r="U267" t="s">
+    <row r="263" spans="22:22">
+      <c r="V263" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="268" spans="21:21">
-      <c r="U268" t="s">
+    <row r="264" spans="22:22">
+      <c r="V264" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="269" spans="21:21">
-      <c r="U269" t="s">
+    <row r="265" spans="22:22">
+      <c r="V265" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="270" spans="21:21">
-      <c r="U270" t="s">
+    <row r="266" spans="22:22">
+      <c r="V266" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="271" spans="21:21">
-      <c r="U271" t="s">
+    <row r="267" spans="22:22">
+      <c r="V267" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="272" spans="21:21">
-      <c r="U272" t="s">
+    <row r="268" spans="22:22">
+      <c r="V268" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="273" spans="21:21">
-      <c r="U273" t="s">
+    <row r="269" spans="22:22">
+      <c r="V269" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="274" spans="21:21">
-      <c r="U274" t="s">
+    <row r="270" spans="22:22">
+      <c r="V270" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="275" spans="21:21">
-      <c r="U275" t="s">
+    <row r="271" spans="22:22">
+      <c r="V271" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="276" spans="21:21">
-      <c r="U276" t="s">
+    <row r="272" spans="22:22">
+      <c r="V272" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="277" spans="21:21">
-      <c r="U277" t="s">
+    <row r="273" spans="22:22">
+      <c r="V273" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="278" spans="21:21">
-      <c r="U278" t="s">
+    <row r="274" spans="22:22">
+      <c r="V274" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="279" spans="21:21">
-      <c r="U279" t="s">
+    <row r="275" spans="22:22">
+      <c r="V275" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="280" spans="21:21">
-      <c r="U280" t="s">
+    <row r="276" spans="22:22">
+      <c r="V276" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="281" spans="21:21">
-      <c r="U281" t="s">
+    <row r="277" spans="22:22">
+      <c r="V277" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="282" spans="21:21">
-      <c r="U282" t="s">
+    <row r="278" spans="22:22">
+      <c r="V278" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="283" spans="21:21">
-      <c r="U283" t="s">
+    <row r="279" spans="22:22">
+      <c r="V279" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="284" spans="21:21">
-      <c r="U284" t="s">
+    <row r="280" spans="22:22">
+      <c r="V280" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="285" spans="21:21">
-      <c r="U285" t="s">
+    <row r="281" spans="22:22">
+      <c r="V281" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="286" spans="21:21">
-      <c r="U286" t="s">
+    <row r="282" spans="22:22">
+      <c r="V282" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="287" spans="21:21">
-      <c r="U287" t="s">
+    <row r="283" spans="22:22">
+      <c r="V283" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="288" spans="21:21">
-      <c r="U288" t="s">
+    <row r="284" spans="22:22">
+      <c r="V284" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="289" spans="21:21">
-      <c r="U289" t="s">
+    <row r="285" spans="22:22">
+      <c r="V285" t="s">
         <v>602</v>
+      </c>
+    </row>
+    <row r="286" spans="22:22">
+      <c r="V286" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="287" spans="22:22">
+      <c r="V287" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="288" spans="22:22">
+      <c r="V288" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="289" spans="22:22">
+      <c r="V289" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="290" spans="22:22">
+      <c r="V290" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="291" spans="22:22">
+      <c r="V291" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="292" spans="22:22">
+      <c r="V292" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="293" spans="22:22">
+      <c r="V293" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="294" spans="22:22">
+      <c r="V294" t="s">
+        <v>611</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000036/metadata_template_ERC000036.xlsx
+++ b/templates/ERC000036/metadata_template_ERC000036.xlsx
@@ -18,9 +18,9 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$V$1:$V$294</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$W$1:$W$294</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
-    <definedName name="investigationtype">'cv_sample'!$M$1:$M$12</definedName>
+    <definedName name="investigationtype">'cv_sample'!$N$1:$N$12</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="630">
   <si>
     <t>alias</t>
   </si>
@@ -848,6 +848,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -3439,13 +3445,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3483,7 +3489,7 @@
         <v>286</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>302</v>
@@ -3510,7 +3516,7 @@
         <v>316</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>612</v>
+        <v>318</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>614</v>
@@ -3533,8 +3539,11 @@
       <c r="AC1" s="1" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" ht="150" customHeight="1">
+      <c r="AD1" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -3572,7 +3581,7 @@
         <v>287</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>303</v>
@@ -3599,7 +3608,7 @@
         <v>317</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>613</v>
+        <v>319</v>
       </c>
       <c r="W2" s="2" t="s">
         <v>615</v>
@@ -3622,13 +3631,16 @@
       <c r="AC2" s="2" t="s">
         <v>627</v>
       </c>
+      <c r="AD2" s="2" t="s">
+        <v>629</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N101">
       <formula1>investigationtype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V3:V101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3:W101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
   </dataValidations>
@@ -3638,1513 +3650,1513 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="M1:V294"/>
+  <dimension ref="N1:W294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="13:22">
-      <c r="M1" t="s">
-        <v>288</v>
-      </c>
-      <c r="V1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="2" spans="13:22">
-      <c r="M2" t="s">
-        <v>289</v>
-      </c>
-      <c r="V2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="3" spans="13:22">
-      <c r="M3" t="s">
+    <row r="1" spans="14:23">
+      <c r="N1" t="s">
         <v>290</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W1" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="4" spans="13:22">
-      <c r="M4" t="s">
+    <row r="2" spans="14:23">
+      <c r="N2" t="s">
         <v>291</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W2" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="5" spans="13:22">
-      <c r="M5" t="s">
+    <row r="3" spans="14:23">
+      <c r="N3" t="s">
         <v>292</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W3" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="6" spans="13:22">
-      <c r="M6" t="s">
+    <row r="4" spans="14:23">
+      <c r="N4" t="s">
         <v>293</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W4" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="7" spans="13:22">
-      <c r="M7" t="s">
+    <row r="5" spans="14:23">
+      <c r="N5" t="s">
         <v>294</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W5" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="8" spans="13:22">
-      <c r="M8" t="s">
+    <row r="6" spans="14:23">
+      <c r="N6" t="s">
         <v>295</v>
       </c>
-      <c r="V8" t="s">
+      <c r="W6" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="9" spans="13:22">
-      <c r="M9" t="s">
+    <row r="7" spans="14:23">
+      <c r="N7" t="s">
         <v>296</v>
       </c>
-      <c r="V9" t="s">
+      <c r="W7" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="10" spans="13:22">
-      <c r="M10" t="s">
+    <row r="8" spans="14:23">
+      <c r="N8" t="s">
         <v>297</v>
       </c>
-      <c r="V10" t="s">
+      <c r="W8" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="11" spans="13:22">
-      <c r="M11" t="s">
+    <row r="9" spans="14:23">
+      <c r="N9" t="s">
         <v>298</v>
       </c>
-      <c r="V11" t="s">
+      <c r="W9" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="12" spans="13:22">
-      <c r="M12" t="s">
+    <row r="10" spans="14:23">
+      <c r="N10" t="s">
         <v>299</v>
       </c>
-      <c r="V12" t="s">
+      <c r="W10" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="13" spans="13:22">
-      <c r="V13" t="s">
+    <row r="11" spans="14:23">
+      <c r="N11" t="s">
+        <v>300</v>
+      </c>
+      <c r="W11" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="14" spans="13:22">
-      <c r="V14" t="s">
+    <row r="12" spans="14:23">
+      <c r="N12" t="s">
+        <v>301</v>
+      </c>
+      <c r="W12" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="15" spans="13:22">
-      <c r="V15" t="s">
+    <row r="13" spans="14:23">
+      <c r="W13" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="16" spans="13:22">
-      <c r="V16" t="s">
+    <row r="14" spans="14:23">
+      <c r="W14" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="17" spans="22:22">
-      <c r="V17" t="s">
+    <row r="15" spans="14:23">
+      <c r="W15" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="18" spans="22:22">
-      <c r="V18" t="s">
+    <row r="16" spans="14:23">
+      <c r="W16" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="19" spans="22:22">
-      <c r="V19" t="s">
+    <row r="17" spans="23:23">
+      <c r="W17" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="20" spans="22:22">
-      <c r="V20" t="s">
+    <row r="18" spans="23:23">
+      <c r="W18" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="21" spans="22:22">
-      <c r="V21" t="s">
+    <row r="19" spans="23:23">
+      <c r="W19" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="22" spans="22:22">
-      <c r="V22" t="s">
+    <row r="20" spans="23:23">
+      <c r="W20" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="23" spans="22:22">
-      <c r="V23" t="s">
+    <row r="21" spans="23:23">
+      <c r="W21" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="24" spans="22:22">
-      <c r="V24" t="s">
+    <row r="22" spans="23:23">
+      <c r="W22" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="25" spans="22:22">
-      <c r="V25" t="s">
+    <row r="23" spans="23:23">
+      <c r="W23" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="26" spans="22:22">
-      <c r="V26" t="s">
+    <row r="24" spans="23:23">
+      <c r="W24" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="27" spans="22:22">
-      <c r="V27" t="s">
+    <row r="25" spans="23:23">
+      <c r="W25" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="28" spans="22:22">
-      <c r="V28" t="s">
+    <row r="26" spans="23:23">
+      <c r="W26" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="29" spans="22:22">
-      <c r="V29" t="s">
+    <row r="27" spans="23:23">
+      <c r="W27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="30" spans="22:22">
-      <c r="V30" t="s">
+    <row r="28" spans="23:23">
+      <c r="W28" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="31" spans="22:22">
-      <c r="V31" t="s">
+    <row r="29" spans="23:23">
+      <c r="W29" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="32" spans="22:22">
-      <c r="V32" t="s">
+    <row r="30" spans="23:23">
+      <c r="W30" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="33" spans="22:22">
-      <c r="V33" t="s">
+    <row r="31" spans="23:23">
+      <c r="W31" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="34" spans="22:22">
-      <c r="V34" t="s">
+    <row r="32" spans="23:23">
+      <c r="W32" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="35" spans="22:22">
-      <c r="V35" t="s">
+    <row r="33" spans="23:23">
+      <c r="W33" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="36" spans="22:22">
-      <c r="V36" t="s">
+    <row r="34" spans="23:23">
+      <c r="W34" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="37" spans="22:22">
-      <c r="V37" t="s">
+    <row r="35" spans="23:23">
+      <c r="W35" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="38" spans="22:22">
-      <c r="V38" t="s">
+    <row r="36" spans="23:23">
+      <c r="W36" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="39" spans="22:22">
-      <c r="V39" t="s">
+    <row r="37" spans="23:23">
+      <c r="W37" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="40" spans="22:22">
-      <c r="V40" t="s">
+    <row r="38" spans="23:23">
+      <c r="W38" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="41" spans="22:22">
-      <c r="V41" t="s">
+    <row r="39" spans="23:23">
+      <c r="W39" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="42" spans="22:22">
-      <c r="V42" t="s">
+    <row r="40" spans="23:23">
+      <c r="W40" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="43" spans="22:22">
-      <c r="V43" t="s">
+    <row r="41" spans="23:23">
+      <c r="W41" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="44" spans="22:22">
-      <c r="V44" t="s">
+    <row r="42" spans="23:23">
+      <c r="W42" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="45" spans="22:22">
-      <c r="V45" t="s">
+    <row r="43" spans="23:23">
+      <c r="W43" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="46" spans="22:22">
-      <c r="V46" t="s">
+    <row r="44" spans="23:23">
+      <c r="W44" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="47" spans="22:22">
-      <c r="V47" t="s">
+    <row r="45" spans="23:23">
+      <c r="W45" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="48" spans="22:22">
-      <c r="V48" t="s">
+    <row r="46" spans="23:23">
+      <c r="W46" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="49" spans="22:22">
-      <c r="V49" t="s">
+    <row r="47" spans="23:23">
+      <c r="W47" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="50" spans="22:22">
-      <c r="V50" t="s">
+    <row r="48" spans="23:23">
+      <c r="W48" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="51" spans="22:22">
-      <c r="V51" t="s">
+    <row r="49" spans="23:23">
+      <c r="W49" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="52" spans="22:22">
-      <c r="V52" t="s">
+    <row r="50" spans="23:23">
+      <c r="W50" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="53" spans="22:22">
-      <c r="V53" t="s">
+    <row r="51" spans="23:23">
+      <c r="W51" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="54" spans="22:22">
-      <c r="V54" t="s">
+    <row r="52" spans="23:23">
+      <c r="W52" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="55" spans="22:22">
-      <c r="V55" t="s">
+    <row r="53" spans="23:23">
+      <c r="W53" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="56" spans="22:22">
-      <c r="V56" t="s">
+    <row r="54" spans="23:23">
+      <c r="W54" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="57" spans="22:22">
-      <c r="V57" t="s">
+    <row r="55" spans="23:23">
+      <c r="W55" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="58" spans="22:22">
-      <c r="V58" t="s">
+    <row r="56" spans="23:23">
+      <c r="W56" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="59" spans="22:22">
-      <c r="V59" t="s">
+    <row r="57" spans="23:23">
+      <c r="W57" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="60" spans="22:22">
-      <c r="V60" t="s">
+    <row r="58" spans="23:23">
+      <c r="W58" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="61" spans="22:22">
-      <c r="V61" t="s">
+    <row r="59" spans="23:23">
+      <c r="W59" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="62" spans="22:22">
-      <c r="V62" t="s">
+    <row r="60" spans="23:23">
+      <c r="W60" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="63" spans="22:22">
-      <c r="V63" t="s">
+    <row r="61" spans="23:23">
+      <c r="W61" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="64" spans="22:22">
-      <c r="V64" t="s">
+    <row r="62" spans="23:23">
+      <c r="W62" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="65" spans="22:22">
-      <c r="V65" t="s">
+    <row r="63" spans="23:23">
+      <c r="W63" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="66" spans="22:22">
-      <c r="V66" t="s">
+    <row r="64" spans="23:23">
+      <c r="W64" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="67" spans="22:22">
-      <c r="V67" t="s">
+    <row r="65" spans="23:23">
+      <c r="W65" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="68" spans="22:22">
-      <c r="V68" t="s">
+    <row r="66" spans="23:23">
+      <c r="W66" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="69" spans="22:22">
-      <c r="V69" t="s">
+    <row r="67" spans="23:23">
+      <c r="W67" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="70" spans="22:22">
-      <c r="V70" t="s">
+    <row r="68" spans="23:23">
+      <c r="W68" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="71" spans="22:22">
-      <c r="V71" t="s">
+    <row r="69" spans="23:23">
+      <c r="W69" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="72" spans="22:22">
-      <c r="V72" t="s">
+    <row r="70" spans="23:23">
+      <c r="W70" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="73" spans="22:22">
-      <c r="V73" t="s">
+    <row r="71" spans="23:23">
+      <c r="W71" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="74" spans="22:22">
-      <c r="V74" t="s">
+    <row r="72" spans="23:23">
+      <c r="W72" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="75" spans="22:22">
-      <c r="V75" t="s">
+    <row r="73" spans="23:23">
+      <c r="W73" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="76" spans="22:22">
-      <c r="V76" t="s">
+    <row r="74" spans="23:23">
+      <c r="W74" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="77" spans="22:22">
-      <c r="V77" t="s">
+    <row r="75" spans="23:23">
+      <c r="W75" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="78" spans="22:22">
-      <c r="V78" t="s">
+    <row r="76" spans="23:23">
+      <c r="W76" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="79" spans="22:22">
-      <c r="V79" t="s">
+    <row r="77" spans="23:23">
+      <c r="W77" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="80" spans="22:22">
-      <c r="V80" t="s">
+    <row r="78" spans="23:23">
+      <c r="W78" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="81" spans="22:22">
-      <c r="V81" t="s">
+    <row r="79" spans="23:23">
+      <c r="W79" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="82" spans="22:22">
-      <c r="V82" t="s">
+    <row r="80" spans="23:23">
+      <c r="W80" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="83" spans="22:22">
-      <c r="V83" t="s">
+    <row r="81" spans="23:23">
+      <c r="W81" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="22:22">
-      <c r="V84" t="s">
+    <row r="82" spans="23:23">
+      <c r="W82" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="85" spans="22:22">
-      <c r="V85" t="s">
+    <row r="83" spans="23:23">
+      <c r="W83" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="86" spans="22:22">
-      <c r="V86" t="s">
+    <row r="84" spans="23:23">
+      <c r="W84" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="87" spans="22:22">
-      <c r="V87" t="s">
+    <row r="85" spans="23:23">
+      <c r="W85" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="88" spans="22:22">
-      <c r="V88" t="s">
+    <row r="86" spans="23:23">
+      <c r="W86" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="89" spans="22:22">
-      <c r="V89" t="s">
+    <row r="87" spans="23:23">
+      <c r="W87" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="90" spans="22:22">
-      <c r="V90" t="s">
+    <row r="88" spans="23:23">
+      <c r="W88" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="91" spans="22:22">
-      <c r="V91" t="s">
+    <row r="89" spans="23:23">
+      <c r="W89" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="92" spans="22:22">
-      <c r="V92" t="s">
+    <row r="90" spans="23:23">
+      <c r="W90" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="93" spans="22:22">
-      <c r="V93" t="s">
+    <row r="91" spans="23:23">
+      <c r="W91" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="94" spans="22:22">
-      <c r="V94" t="s">
+    <row r="92" spans="23:23">
+      <c r="W92" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="95" spans="22:22">
-      <c r="V95" t="s">
+    <row r="93" spans="23:23">
+      <c r="W93" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="96" spans="22:22">
-      <c r="V96" t="s">
+    <row r="94" spans="23:23">
+      <c r="W94" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="97" spans="22:22">
-      <c r="V97" t="s">
+    <row r="95" spans="23:23">
+      <c r="W95" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="98" spans="22:22">
-      <c r="V98" t="s">
+    <row r="96" spans="23:23">
+      <c r="W96" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="99" spans="22:22">
-      <c r="V99" t="s">
+    <row r="97" spans="23:23">
+      <c r="W97" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="100" spans="22:22">
-      <c r="V100" t="s">
+    <row r="98" spans="23:23">
+      <c r="W98" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="101" spans="22:22">
-      <c r="V101" t="s">
+    <row r="99" spans="23:23">
+      <c r="W99" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="102" spans="22:22">
-      <c r="V102" t="s">
+    <row r="100" spans="23:23">
+      <c r="W100" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="103" spans="22:22">
-      <c r="V103" t="s">
+    <row r="101" spans="23:23">
+      <c r="W101" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="104" spans="22:22">
-      <c r="V104" t="s">
+    <row r="102" spans="23:23">
+      <c r="W102" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="105" spans="22:22">
-      <c r="V105" t="s">
+    <row r="103" spans="23:23">
+      <c r="W103" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="106" spans="22:22">
-      <c r="V106" t="s">
+    <row r="104" spans="23:23">
+      <c r="W104" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="107" spans="22:22">
-      <c r="V107" t="s">
+    <row r="105" spans="23:23">
+      <c r="W105" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="108" spans="22:22">
-      <c r="V108" t="s">
+    <row r="106" spans="23:23">
+      <c r="W106" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="109" spans="22:22">
-      <c r="V109" t="s">
+    <row r="107" spans="23:23">
+      <c r="W107" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="110" spans="22:22">
-      <c r="V110" t="s">
+    <row r="108" spans="23:23">
+      <c r="W108" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="111" spans="22:22">
-      <c r="V111" t="s">
+    <row r="109" spans="23:23">
+      <c r="W109" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="112" spans="22:22">
-      <c r="V112" t="s">
+    <row r="110" spans="23:23">
+      <c r="W110" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="113" spans="22:22">
-      <c r="V113" t="s">
+    <row r="111" spans="23:23">
+      <c r="W111" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="114" spans="22:22">
-      <c r="V114" t="s">
+    <row r="112" spans="23:23">
+      <c r="W112" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="115" spans="22:22">
-      <c r="V115" t="s">
+    <row r="113" spans="23:23">
+      <c r="W113" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="116" spans="22:22">
-      <c r="V116" t="s">
+    <row r="114" spans="23:23">
+      <c r="W114" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="117" spans="22:22">
-      <c r="V117" t="s">
+    <row r="115" spans="23:23">
+      <c r="W115" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="118" spans="22:22">
-      <c r="V118" t="s">
+    <row r="116" spans="23:23">
+      <c r="W116" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="119" spans="22:22">
-      <c r="V119" t="s">
+    <row r="117" spans="23:23">
+      <c r="W117" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="120" spans="22:22">
-      <c r="V120" t="s">
+    <row r="118" spans="23:23">
+      <c r="W118" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="121" spans="22:22">
-      <c r="V121" t="s">
+    <row r="119" spans="23:23">
+      <c r="W119" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="122" spans="22:22">
-      <c r="V122" t="s">
+    <row r="120" spans="23:23">
+      <c r="W120" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="123" spans="22:22">
-      <c r="V123" t="s">
+    <row r="121" spans="23:23">
+      <c r="W121" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="124" spans="22:22">
-      <c r="V124" t="s">
+    <row r="122" spans="23:23">
+      <c r="W122" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="125" spans="22:22">
-      <c r="V125" t="s">
+    <row r="123" spans="23:23">
+      <c r="W123" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="126" spans="22:22">
-      <c r="V126" t="s">
+    <row r="124" spans="23:23">
+      <c r="W124" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="127" spans="22:22">
-      <c r="V127" t="s">
+    <row r="125" spans="23:23">
+      <c r="W125" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="128" spans="22:22">
-      <c r="V128" t="s">
+    <row r="126" spans="23:23">
+      <c r="W126" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="129" spans="22:22">
-      <c r="V129" t="s">
+    <row r="127" spans="23:23">
+      <c r="W127" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="130" spans="22:22">
-      <c r="V130" t="s">
+    <row r="128" spans="23:23">
+      <c r="W128" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="131" spans="22:22">
-      <c r="V131" t="s">
+    <row r="129" spans="23:23">
+      <c r="W129" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="132" spans="22:22">
-      <c r="V132" t="s">
+    <row r="130" spans="23:23">
+      <c r="W130" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="133" spans="22:22">
-      <c r="V133" t="s">
+    <row r="131" spans="23:23">
+      <c r="W131" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="134" spans="22:22">
-      <c r="V134" t="s">
+    <row r="132" spans="23:23">
+      <c r="W132" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="135" spans="22:22">
-      <c r="V135" t="s">
+    <row r="133" spans="23:23">
+      <c r="W133" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="136" spans="22:22">
-      <c r="V136" t="s">
+    <row r="134" spans="23:23">
+      <c r="W134" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="137" spans="22:22">
-      <c r="V137" t="s">
+    <row r="135" spans="23:23">
+      <c r="W135" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="138" spans="22:22">
-      <c r="V138" t="s">
+    <row r="136" spans="23:23">
+      <c r="W136" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="139" spans="22:22">
-      <c r="V139" t="s">
+    <row r="137" spans="23:23">
+      <c r="W137" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="140" spans="22:22">
-      <c r="V140" t="s">
+    <row r="138" spans="23:23">
+      <c r="W138" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="141" spans="22:22">
-      <c r="V141" t="s">
+    <row r="139" spans="23:23">
+      <c r="W139" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="142" spans="22:22">
-      <c r="V142" t="s">
+    <row r="140" spans="23:23">
+      <c r="W140" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="143" spans="22:22">
-      <c r="V143" t="s">
+    <row r="141" spans="23:23">
+      <c r="W141" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="144" spans="22:22">
-      <c r="V144" t="s">
+    <row r="142" spans="23:23">
+      <c r="W142" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="145" spans="22:22">
-      <c r="V145" t="s">
+    <row r="143" spans="23:23">
+      <c r="W143" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="146" spans="22:22">
-      <c r="V146" t="s">
+    <row r="144" spans="23:23">
+      <c r="W144" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="147" spans="22:22">
-      <c r="V147" t="s">
+    <row r="145" spans="23:23">
+      <c r="W145" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="148" spans="22:22">
-      <c r="V148" t="s">
+    <row r="146" spans="23:23">
+      <c r="W146" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="149" spans="22:22">
-      <c r="V149" t="s">
+    <row r="147" spans="23:23">
+      <c r="W147" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="150" spans="22:22">
-      <c r="V150" t="s">
+    <row r="148" spans="23:23">
+      <c r="W148" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="151" spans="22:22">
-      <c r="V151" t="s">
+    <row r="149" spans="23:23">
+      <c r="W149" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="152" spans="22:22">
-      <c r="V152" t="s">
+    <row r="150" spans="23:23">
+      <c r="W150" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="153" spans="22:22">
-      <c r="V153" t="s">
+    <row r="151" spans="23:23">
+      <c r="W151" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="154" spans="22:22">
-      <c r="V154" t="s">
+    <row r="152" spans="23:23">
+      <c r="W152" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="155" spans="22:22">
-      <c r="V155" t="s">
+    <row r="153" spans="23:23">
+      <c r="W153" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="156" spans="22:22">
-      <c r="V156" t="s">
+    <row r="154" spans="23:23">
+      <c r="W154" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="157" spans="22:22">
-      <c r="V157" t="s">
+    <row r="155" spans="23:23">
+      <c r="W155" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="158" spans="22:22">
-      <c r="V158" t="s">
+    <row r="156" spans="23:23">
+      <c r="W156" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="159" spans="22:22">
-      <c r="V159" t="s">
+    <row r="157" spans="23:23">
+      <c r="W157" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="160" spans="22:22">
-      <c r="V160" t="s">
+    <row r="158" spans="23:23">
+      <c r="W158" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="161" spans="22:22">
-      <c r="V161" t="s">
+    <row r="159" spans="23:23">
+      <c r="W159" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="162" spans="22:22">
-      <c r="V162" t="s">
+    <row r="160" spans="23:23">
+      <c r="W160" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="163" spans="22:22">
-      <c r="V163" t="s">
+    <row r="161" spans="23:23">
+      <c r="W161" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="164" spans="22:22">
-      <c r="V164" t="s">
+    <row r="162" spans="23:23">
+      <c r="W162" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="165" spans="22:22">
-      <c r="V165" t="s">
+    <row r="163" spans="23:23">
+      <c r="W163" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="166" spans="22:22">
-      <c r="V166" t="s">
+    <row r="164" spans="23:23">
+      <c r="W164" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="167" spans="22:22">
-      <c r="V167" t="s">
+    <row r="165" spans="23:23">
+      <c r="W165" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="168" spans="22:22">
-      <c r="V168" t="s">
+    <row r="166" spans="23:23">
+      <c r="W166" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="169" spans="22:22">
-      <c r="V169" t="s">
+    <row r="167" spans="23:23">
+      <c r="W167" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="170" spans="22:22">
-      <c r="V170" t="s">
+    <row r="168" spans="23:23">
+      <c r="W168" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="171" spans="22:22">
-      <c r="V171" t="s">
+    <row r="169" spans="23:23">
+      <c r="W169" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="172" spans="22:22">
-      <c r="V172" t="s">
+    <row r="170" spans="23:23">
+      <c r="W170" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="173" spans="22:22">
-      <c r="V173" t="s">
+    <row r="171" spans="23:23">
+      <c r="W171" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="174" spans="22:22">
-      <c r="V174" t="s">
+    <row r="172" spans="23:23">
+      <c r="W172" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="175" spans="22:22">
-      <c r="V175" t="s">
+    <row r="173" spans="23:23">
+      <c r="W173" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="176" spans="22:22">
-      <c r="V176" t="s">
+    <row r="174" spans="23:23">
+      <c r="W174" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="177" spans="22:22">
-      <c r="V177" t="s">
+    <row r="175" spans="23:23">
+      <c r="W175" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="178" spans="22:22">
-      <c r="V178" t="s">
+    <row r="176" spans="23:23">
+      <c r="W176" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="179" spans="22:22">
-      <c r="V179" t="s">
+    <row r="177" spans="23:23">
+      <c r="W177" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="180" spans="22:22">
-      <c r="V180" t="s">
+    <row r="178" spans="23:23">
+      <c r="W178" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="181" spans="22:22">
-      <c r="V181" t="s">
+    <row r="179" spans="23:23">
+      <c r="W179" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="182" spans="22:22">
-      <c r="V182" t="s">
+    <row r="180" spans="23:23">
+      <c r="W180" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="183" spans="22:22">
-      <c r="V183" t="s">
+    <row r="181" spans="23:23">
+      <c r="W181" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="184" spans="22:22">
-      <c r="V184" t="s">
+    <row r="182" spans="23:23">
+      <c r="W182" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="185" spans="22:22">
-      <c r="V185" t="s">
+    <row r="183" spans="23:23">
+      <c r="W183" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="186" spans="22:22">
-      <c r="V186" t="s">
+    <row r="184" spans="23:23">
+      <c r="W184" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="187" spans="22:22">
-      <c r="V187" t="s">
+    <row r="185" spans="23:23">
+      <c r="W185" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="188" spans="22:22">
-      <c r="V188" t="s">
+    <row r="186" spans="23:23">
+      <c r="W186" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="189" spans="22:22">
-      <c r="V189" t="s">
+    <row r="187" spans="23:23">
+      <c r="W187" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="190" spans="22:22">
-      <c r="V190" t="s">
+    <row r="188" spans="23:23">
+      <c r="W188" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="191" spans="22:22">
-      <c r="V191" t="s">
+    <row r="189" spans="23:23">
+      <c r="W189" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="192" spans="22:22">
-      <c r="V192" t="s">
+    <row r="190" spans="23:23">
+      <c r="W190" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="193" spans="22:22">
-      <c r="V193" t="s">
+    <row r="191" spans="23:23">
+      <c r="W191" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="194" spans="22:22">
-      <c r="V194" t="s">
+    <row r="192" spans="23:23">
+      <c r="W192" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="195" spans="22:22">
-      <c r="V195" t="s">
+    <row r="193" spans="23:23">
+      <c r="W193" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="196" spans="22:22">
-      <c r="V196" t="s">
+    <row r="194" spans="23:23">
+      <c r="W194" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="197" spans="22:22">
-      <c r="V197" t="s">
+    <row r="195" spans="23:23">
+      <c r="W195" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="198" spans="22:22">
-      <c r="V198" t="s">
+    <row r="196" spans="23:23">
+      <c r="W196" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="199" spans="22:22">
-      <c r="V199" t="s">
+    <row r="197" spans="23:23">
+      <c r="W197" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="200" spans="22:22">
-      <c r="V200" t="s">
+    <row r="198" spans="23:23">
+      <c r="W198" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="201" spans="22:22">
-      <c r="V201" t="s">
+    <row r="199" spans="23:23">
+      <c r="W199" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="202" spans="22:22">
-      <c r="V202" t="s">
+    <row r="200" spans="23:23">
+      <c r="W200" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="203" spans="22:22">
-      <c r="V203" t="s">
+    <row r="201" spans="23:23">
+      <c r="W201" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="204" spans="22:22">
-      <c r="V204" t="s">
+    <row r="202" spans="23:23">
+      <c r="W202" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="205" spans="22:22">
-      <c r="V205" t="s">
+    <row r="203" spans="23:23">
+      <c r="W203" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="206" spans="22:22">
-      <c r="V206" t="s">
+    <row r="204" spans="23:23">
+      <c r="W204" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="207" spans="22:22">
-      <c r="V207" t="s">
+    <row r="205" spans="23:23">
+      <c r="W205" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="208" spans="22:22">
-      <c r="V208" t="s">
+    <row r="206" spans="23:23">
+      <c r="W206" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="209" spans="22:22">
-      <c r="V209" t="s">
+    <row r="207" spans="23:23">
+      <c r="W207" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="210" spans="22:22">
-      <c r="V210" t="s">
+    <row r="208" spans="23:23">
+      <c r="W208" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="211" spans="22:22">
-      <c r="V211" t="s">
+    <row r="209" spans="23:23">
+      <c r="W209" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="212" spans="22:22">
-      <c r="V212" t="s">
+    <row r="210" spans="23:23">
+      <c r="W210" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="213" spans="22:22">
-      <c r="V213" t="s">
+    <row r="211" spans="23:23">
+      <c r="W211" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="214" spans="22:22">
-      <c r="V214" t="s">
+    <row r="212" spans="23:23">
+      <c r="W212" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="215" spans="22:22">
-      <c r="V215" t="s">
+    <row r="213" spans="23:23">
+      <c r="W213" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="216" spans="22:22">
-      <c r="V216" t="s">
+    <row r="214" spans="23:23">
+      <c r="W214" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="217" spans="22:22">
-      <c r="V217" t="s">
+    <row r="215" spans="23:23">
+      <c r="W215" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="218" spans="22:22">
-      <c r="V218" t="s">
+    <row r="216" spans="23:23">
+      <c r="W216" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="219" spans="22:22">
-      <c r="V219" t="s">
+    <row r="217" spans="23:23">
+      <c r="W217" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="220" spans="22:22">
-      <c r="V220" t="s">
+    <row r="218" spans="23:23">
+      <c r="W218" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="221" spans="22:22">
-      <c r="V221" t="s">
+    <row r="219" spans="23:23">
+      <c r="W219" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="222" spans="22:22">
-      <c r="V222" t="s">
+    <row r="220" spans="23:23">
+      <c r="W220" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="223" spans="22:22">
-      <c r="V223" t="s">
+    <row r="221" spans="23:23">
+      <c r="W221" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="224" spans="22:22">
-      <c r="V224" t="s">
+    <row r="222" spans="23:23">
+      <c r="W222" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="225" spans="22:22">
-      <c r="V225" t="s">
+    <row r="223" spans="23:23">
+      <c r="W223" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="226" spans="22:22">
-      <c r="V226" t="s">
+    <row r="224" spans="23:23">
+      <c r="W224" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="227" spans="22:22">
-      <c r="V227" t="s">
+    <row r="225" spans="23:23">
+      <c r="W225" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="228" spans="22:22">
-      <c r="V228" t="s">
+    <row r="226" spans="23:23">
+      <c r="W226" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="229" spans="22:22">
-      <c r="V229" t="s">
+    <row r="227" spans="23:23">
+      <c r="W227" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="230" spans="22:22">
-      <c r="V230" t="s">
+    <row r="228" spans="23:23">
+      <c r="W228" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="231" spans="22:22">
-      <c r="V231" t="s">
+    <row r="229" spans="23:23">
+      <c r="W229" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="232" spans="22:22">
-      <c r="V232" t="s">
+    <row r="230" spans="23:23">
+      <c r="W230" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="233" spans="22:22">
-      <c r="V233" t="s">
+    <row r="231" spans="23:23">
+      <c r="W231" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="234" spans="22:22">
-      <c r="V234" t="s">
+    <row r="232" spans="23:23">
+      <c r="W232" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="235" spans="22:22">
-      <c r="V235" t="s">
+    <row r="233" spans="23:23">
+      <c r="W233" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="236" spans="22:22">
-      <c r="V236" t="s">
+    <row r="234" spans="23:23">
+      <c r="W234" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="237" spans="22:22">
-      <c r="V237" t="s">
+    <row r="235" spans="23:23">
+      <c r="W235" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="238" spans="22:22">
-      <c r="V238" t="s">
+    <row r="236" spans="23:23">
+      <c r="W236" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="239" spans="22:22">
-      <c r="V239" t="s">
+    <row r="237" spans="23:23">
+      <c r="W237" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="240" spans="22:22">
-      <c r="V240" t="s">
+    <row r="238" spans="23:23">
+      <c r="W238" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="241" spans="22:22">
-      <c r="V241" t="s">
+    <row r="239" spans="23:23">
+      <c r="W239" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="242" spans="22:22">
-      <c r="V242" t="s">
+    <row r="240" spans="23:23">
+      <c r="W240" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="243" spans="22:22">
-      <c r="V243" t="s">
+    <row r="241" spans="23:23">
+      <c r="W241" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="244" spans="22:22">
-      <c r="V244" t="s">
+    <row r="242" spans="23:23">
+      <c r="W242" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="245" spans="22:22">
-      <c r="V245" t="s">
+    <row r="243" spans="23:23">
+      <c r="W243" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="246" spans="22:22">
-      <c r="V246" t="s">
+    <row r="244" spans="23:23">
+      <c r="W244" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="247" spans="22:22">
-      <c r="V247" t="s">
+    <row r="245" spans="23:23">
+      <c r="W245" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="248" spans="22:22">
-      <c r="V248" t="s">
+    <row r="246" spans="23:23">
+      <c r="W246" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="249" spans="22:22">
-      <c r="V249" t="s">
+    <row r="247" spans="23:23">
+      <c r="W247" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="250" spans="22:22">
-      <c r="V250" t="s">
+    <row r="248" spans="23:23">
+      <c r="W248" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="251" spans="22:22">
-      <c r="V251" t="s">
+    <row r="249" spans="23:23">
+      <c r="W249" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="252" spans="22:22">
-      <c r="V252" t="s">
+    <row r="250" spans="23:23">
+      <c r="W250" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="253" spans="22:22">
-      <c r="V253" t="s">
+    <row r="251" spans="23:23">
+      <c r="W251" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="254" spans="22:22">
-      <c r="V254" t="s">
+    <row r="252" spans="23:23">
+      <c r="W252" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="255" spans="22:22">
-      <c r="V255" t="s">
+    <row r="253" spans="23:23">
+      <c r="W253" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="256" spans="22:22">
-      <c r="V256" t="s">
+    <row r="254" spans="23:23">
+      <c r="W254" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="257" spans="22:22">
-      <c r="V257" t="s">
+    <row r="255" spans="23:23">
+      <c r="W255" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="258" spans="22:22">
-      <c r="V258" t="s">
+    <row r="256" spans="23:23">
+      <c r="W256" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="259" spans="22:22">
-      <c r="V259" t="s">
+    <row r="257" spans="23:23">
+      <c r="W257" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="260" spans="22:22">
-      <c r="V260" t="s">
+    <row r="258" spans="23:23">
+      <c r="W258" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="261" spans="22:22">
-      <c r="V261" t="s">
+    <row r="259" spans="23:23">
+      <c r="W259" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="262" spans="22:22">
-      <c r="V262" t="s">
+    <row r="260" spans="23:23">
+      <c r="W260" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="263" spans="22:22">
-      <c r="V263" t="s">
+    <row r="261" spans="23:23">
+      <c r="W261" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="264" spans="22:22">
-      <c r="V264" t="s">
+    <row r="262" spans="23:23">
+      <c r="W262" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="265" spans="22:22">
-      <c r="V265" t="s">
+    <row r="263" spans="23:23">
+      <c r="W263" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="266" spans="22:22">
-      <c r="V266" t="s">
+    <row r="264" spans="23:23">
+      <c r="W264" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="267" spans="22:22">
-      <c r="V267" t="s">
+    <row r="265" spans="23:23">
+      <c r="W265" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="268" spans="22:22">
-      <c r="V268" t="s">
+    <row r="266" spans="23:23">
+      <c r="W266" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="269" spans="22:22">
-      <c r="V269" t="s">
+    <row r="267" spans="23:23">
+      <c r="W267" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="270" spans="22:22">
-      <c r="V270" t="s">
+    <row r="268" spans="23:23">
+      <c r="W268" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="271" spans="22:22">
-      <c r="V271" t="s">
+    <row r="269" spans="23:23">
+      <c r="W269" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="272" spans="22:22">
-      <c r="V272" t="s">
+    <row r="270" spans="23:23">
+      <c r="W270" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="273" spans="22:22">
-      <c r="V273" t="s">
+    <row r="271" spans="23:23">
+      <c r="W271" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="274" spans="22:22">
-      <c r="V274" t="s">
+    <row r="272" spans="23:23">
+      <c r="W272" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="275" spans="22:22">
-      <c r="V275" t="s">
+    <row r="273" spans="23:23">
+      <c r="W273" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="276" spans="22:22">
-      <c r="V276" t="s">
+    <row r="274" spans="23:23">
+      <c r="W274" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="277" spans="22:22">
-      <c r="V277" t="s">
+    <row r="275" spans="23:23">
+      <c r="W275" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="278" spans="22:22">
-      <c r="V278" t="s">
+    <row r="276" spans="23:23">
+      <c r="W276" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="279" spans="22:22">
-      <c r="V279" t="s">
+    <row r="277" spans="23:23">
+      <c r="W277" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="280" spans="22:22">
-      <c r="V280" t="s">
+    <row r="278" spans="23:23">
+      <c r="W278" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="281" spans="22:22">
-      <c r="V281" t="s">
+    <row r="279" spans="23:23">
+      <c r="W279" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="282" spans="22:22">
-      <c r="V282" t="s">
+    <row r="280" spans="23:23">
+      <c r="W280" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="283" spans="22:22">
-      <c r="V283" t="s">
+    <row r="281" spans="23:23">
+      <c r="W281" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="284" spans="22:22">
-      <c r="V284" t="s">
+    <row r="282" spans="23:23">
+      <c r="W282" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="285" spans="22:22">
-      <c r="V285" t="s">
+    <row r="283" spans="23:23">
+      <c r="W283" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="286" spans="22:22">
-      <c r="V286" t="s">
+    <row r="284" spans="23:23">
+      <c r="W284" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="287" spans="22:22">
-      <c r="V287" t="s">
+    <row r="285" spans="23:23">
+      <c r="W285" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="288" spans="22:22">
-      <c r="V288" t="s">
+    <row r="286" spans="23:23">
+      <c r="W286" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="289" spans="22:22">
-      <c r="V289" t="s">
+    <row r="287" spans="23:23">
+      <c r="W287" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="290" spans="22:22">
-      <c r="V290" t="s">
+    <row r="288" spans="23:23">
+      <c r="W288" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="291" spans="22:22">
-      <c r="V291" t="s">
+    <row r="289" spans="23:23">
+      <c r="W289" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="292" spans="22:22">
-      <c r="V292" t="s">
+    <row r="290" spans="23:23">
+      <c r="W290" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="293" spans="22:22">
-      <c r="V293" t="s">
+    <row r="291" spans="23:23">
+      <c r="W291" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="294" spans="22:22">
-      <c r="V294" t="s">
+    <row r="292" spans="23:23">
+      <c r="W292" t="s">
         <v>611</v>
+      </c>
+    </row>
+    <row r="293" spans="23:23">
+      <c r="W293" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="294" spans="23:23">
+      <c r="W294" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000036/metadata_template_ERC000036.xlsx
+++ b/templates/ERC000036/metadata_template_ERC000036.xlsx
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$W$1:$W$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$W$1:$W$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="investigationtype">'cv_sample'!$N$1:$N$12</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="630">
   <si>
     <t>alias</t>
   </si>
@@ -448,6 +448,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -538,6 +541,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1201,9 +1207,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1222,6 +1225,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1423,6 +1429,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1432,9 +1441,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1474,7 +1480,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1543,6 +1549,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1618,6 +1627,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1639,6 +1651,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1684,6 +1699,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1696,6 +1714,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1705,9 +1726,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1732,6 +1750,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1792,10 +1813,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -2427,10 +2448,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2471,10 +2492,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2501,7 +2522,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2518,7 +2539,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2535,7 +2556,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2552,7 +2573,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2569,7 +2590,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2586,7 +2607,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2603,7 +2624,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2620,7 +2641,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2637,7 +2658,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2654,7 +2675,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2668,7 +2689,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2682,7 +2703,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2696,7 +2717,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2710,7 +2731,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2724,7 +2745,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2738,7 +2759,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2752,7 +2773,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2766,7 +2787,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2776,8 +2797,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2788,7 +2812,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2799,7 +2823,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -2810,7 +2834,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -2821,7 +2845,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -2832,7 +2856,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -2843,7 +2867,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -2854,7 +2878,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -2865,7 +2889,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -2876,7 +2900,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -2887,7 +2911,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -2898,7 +2922,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -2909,7 +2933,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -2920,7 +2944,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -2928,7 +2952,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -2936,7 +2960,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -2944,7 +2968,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -2952,7 +2976,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -2960,7 +2984,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -2968,7 +2992,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -2976,7 +3000,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -2984,7 +3008,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -2992,7 +3016,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3000,236 +3024,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3251,27 +3280,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3291,122 +3320,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3430,180 +3459,180 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -3621,1488 +3650,1513 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="N1:W289"/>
+  <dimension ref="N1:W294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="14:23">
       <c r="N1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="W1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="14:23">
       <c r="N2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="W2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="14:23">
       <c r="N3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="W3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="14:23">
       <c r="N4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="W4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="14:23">
       <c r="N5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="W5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="14:23">
       <c r="N6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="W6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="14:23">
       <c r="N7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="W7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="14:23">
       <c r="N8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="W8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" spans="14:23">
       <c r="N9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="W9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" spans="14:23">
       <c r="N10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="W10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="14:23">
       <c r="N11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="W11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="14:23">
       <c r="N12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="W12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="14:23">
       <c r="W13" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" spans="14:23">
       <c r="W14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15" spans="14:23">
       <c r="W15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" spans="14:23">
       <c r="W16" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="17" spans="23:23">
       <c r="W17" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" spans="23:23">
       <c r="W18" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="19" spans="23:23">
       <c r="W19" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="20" spans="23:23">
       <c r="W20" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="21" spans="23:23">
       <c r="W21" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="23:23">
       <c r="W22" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23" spans="23:23">
       <c r="W23" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="24" spans="23:23">
       <c r="W24" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="25" spans="23:23">
       <c r="W25" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="23:23">
       <c r="W26" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="23:23">
       <c r="W27" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="28" spans="23:23">
       <c r="W28" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="23:23">
       <c r="W29" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="23:23">
       <c r="W30" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" spans="23:23">
       <c r="W31" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32" spans="23:23">
       <c r="W32" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" spans="23:23">
       <c r="W33" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="34" spans="23:23">
       <c r="W34" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="35" spans="23:23">
       <c r="W35" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="36" spans="23:23">
       <c r="W36" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="37" spans="23:23">
       <c r="W37" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="38" spans="23:23">
       <c r="W38" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="39" spans="23:23">
       <c r="W39" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="40" spans="23:23">
       <c r="W40" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="41" spans="23:23">
       <c r="W41" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="42" spans="23:23">
       <c r="W42" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="43" spans="23:23">
       <c r="W43" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="44" spans="23:23">
       <c r="W44" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="45" spans="23:23">
       <c r="W45" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="46" spans="23:23">
       <c r="W46" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="47" spans="23:23">
       <c r="W47" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="48" spans="23:23">
       <c r="W48" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="49" spans="23:23">
       <c r="W49" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="50" spans="23:23">
       <c r="W50" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="51" spans="23:23">
       <c r="W51" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="52" spans="23:23">
       <c r="W52" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="53" spans="23:23">
       <c r="W53" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="54" spans="23:23">
       <c r="W54" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="55" spans="23:23">
       <c r="W55" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="56" spans="23:23">
       <c r="W56" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="57" spans="23:23">
       <c r="W57" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="58" spans="23:23">
       <c r="W58" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="59" spans="23:23">
       <c r="W59" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="60" spans="23:23">
       <c r="W60" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="61" spans="23:23">
       <c r="W61" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="62" spans="23:23">
       <c r="W62" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="63" spans="23:23">
       <c r="W63" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="64" spans="23:23">
       <c r="W64" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="65" spans="23:23">
       <c r="W65" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="66" spans="23:23">
       <c r="W66" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="67" spans="23:23">
       <c r="W67" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="68" spans="23:23">
       <c r="W68" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="69" spans="23:23">
       <c r="W69" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="70" spans="23:23">
       <c r="W70" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="71" spans="23:23">
       <c r="W71" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="72" spans="23:23">
       <c r="W72" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="73" spans="23:23">
       <c r="W73" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="74" spans="23:23">
       <c r="W74" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="75" spans="23:23">
       <c r="W75" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="76" spans="23:23">
       <c r="W76" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="77" spans="23:23">
       <c r="W77" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="78" spans="23:23">
       <c r="W78" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="79" spans="23:23">
       <c r="W79" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="80" spans="23:23">
       <c r="W80" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="81" spans="23:23">
       <c r="W81" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="82" spans="23:23">
       <c r="W82" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="83" spans="23:23">
       <c r="W83" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="84" spans="23:23">
       <c r="W84" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="85" spans="23:23">
       <c r="W85" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="86" spans="23:23">
       <c r="W86" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="87" spans="23:23">
       <c r="W87" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="88" spans="23:23">
       <c r="W88" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="89" spans="23:23">
       <c r="W89" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="90" spans="23:23">
       <c r="W90" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="91" spans="23:23">
       <c r="W91" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="92" spans="23:23">
       <c r="W92" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="93" spans="23:23">
       <c r="W93" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="94" spans="23:23">
       <c r="W94" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="95" spans="23:23">
       <c r="W95" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="96" spans="23:23">
       <c r="W96" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="97" spans="23:23">
       <c r="W97" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="98" spans="23:23">
       <c r="W98" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="99" spans="23:23">
       <c r="W99" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="100" spans="23:23">
       <c r="W100" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="101" spans="23:23">
       <c r="W101" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="102" spans="23:23">
       <c r="W102" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="103" spans="23:23">
       <c r="W103" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="104" spans="23:23">
       <c r="W104" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="105" spans="23:23">
       <c r="W105" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="106" spans="23:23">
       <c r="W106" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="107" spans="23:23">
       <c r="W107" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="108" spans="23:23">
       <c r="W108" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="109" spans="23:23">
       <c r="W109" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="110" spans="23:23">
       <c r="W110" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="111" spans="23:23">
       <c r="W111" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="112" spans="23:23">
       <c r="W112" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="113" spans="23:23">
       <c r="W113" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="114" spans="23:23">
       <c r="W114" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="115" spans="23:23">
       <c r="W115" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="116" spans="23:23">
       <c r="W116" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="117" spans="23:23">
       <c r="W117" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="118" spans="23:23">
       <c r="W118" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="119" spans="23:23">
       <c r="W119" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="120" spans="23:23">
       <c r="W120" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="121" spans="23:23">
       <c r="W121" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="122" spans="23:23">
       <c r="W122" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="123" spans="23:23">
       <c r="W123" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="124" spans="23:23">
       <c r="W124" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="125" spans="23:23">
       <c r="W125" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="126" spans="23:23">
       <c r="W126" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="127" spans="23:23">
       <c r="W127" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="128" spans="23:23">
       <c r="W128" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="129" spans="23:23">
       <c r="W129" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="130" spans="23:23">
       <c r="W130" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="131" spans="23:23">
       <c r="W131" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="132" spans="23:23">
       <c r="W132" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="133" spans="23:23">
       <c r="W133" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="134" spans="23:23">
       <c r="W134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="135" spans="23:23">
       <c r="W135" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="136" spans="23:23">
       <c r="W136" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="137" spans="23:23">
       <c r="W137" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="138" spans="23:23">
       <c r="W138" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="139" spans="23:23">
       <c r="W139" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="140" spans="23:23">
       <c r="W140" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="141" spans="23:23">
       <c r="W141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="142" spans="23:23">
       <c r="W142" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="143" spans="23:23">
       <c r="W143" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="144" spans="23:23">
       <c r="W144" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="145" spans="23:23">
       <c r="W145" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="146" spans="23:23">
       <c r="W146" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="147" spans="23:23">
       <c r="W147" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="148" spans="23:23">
       <c r="W148" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="149" spans="23:23">
       <c r="W149" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="150" spans="23:23">
       <c r="W150" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="151" spans="23:23">
       <c r="W151" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="152" spans="23:23">
       <c r="W152" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="153" spans="23:23">
       <c r="W153" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="154" spans="23:23">
       <c r="W154" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="155" spans="23:23">
       <c r="W155" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="156" spans="23:23">
       <c r="W156" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="157" spans="23:23">
       <c r="W157" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="158" spans="23:23">
       <c r="W158" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="159" spans="23:23">
       <c r="W159" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="160" spans="23:23">
       <c r="W160" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="161" spans="23:23">
       <c r="W161" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="162" spans="23:23">
       <c r="W162" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="163" spans="23:23">
       <c r="W163" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="164" spans="23:23">
       <c r="W164" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="165" spans="23:23">
       <c r="W165" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="166" spans="23:23">
       <c r="W166" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="167" spans="23:23">
       <c r="W167" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="168" spans="23:23">
       <c r="W168" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="169" spans="23:23">
       <c r="W169" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="170" spans="23:23">
       <c r="W170" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="171" spans="23:23">
       <c r="W171" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="172" spans="23:23">
       <c r="W172" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="173" spans="23:23">
       <c r="W173" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="174" spans="23:23">
       <c r="W174" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="175" spans="23:23">
       <c r="W175" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="176" spans="23:23">
       <c r="W176" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="177" spans="23:23">
       <c r="W177" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="178" spans="23:23">
       <c r="W178" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="179" spans="23:23">
       <c r="W179" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="180" spans="23:23">
       <c r="W180" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="181" spans="23:23">
       <c r="W181" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="182" spans="23:23">
       <c r="W182" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="183" spans="23:23">
       <c r="W183" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="184" spans="23:23">
       <c r="W184" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="185" spans="23:23">
       <c r="W185" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="186" spans="23:23">
       <c r="W186" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="187" spans="23:23">
       <c r="W187" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="188" spans="23:23">
       <c r="W188" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="189" spans="23:23">
       <c r="W189" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="190" spans="23:23">
       <c r="W190" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="191" spans="23:23">
       <c r="W191" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="192" spans="23:23">
       <c r="W192" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="193" spans="23:23">
       <c r="W193" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="194" spans="23:23">
       <c r="W194" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="195" spans="23:23">
       <c r="W195" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="196" spans="23:23">
       <c r="W196" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="197" spans="23:23">
       <c r="W197" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="198" spans="23:23">
       <c r="W198" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="199" spans="23:23">
       <c r="W199" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="200" spans="23:23">
       <c r="W200" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="201" spans="23:23">
       <c r="W201" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="202" spans="23:23">
       <c r="W202" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="203" spans="23:23">
       <c r="W203" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="204" spans="23:23">
       <c r="W204" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="205" spans="23:23">
       <c r="W205" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="206" spans="23:23">
       <c r="W206" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="207" spans="23:23">
       <c r="W207" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="208" spans="23:23">
       <c r="W208" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="209" spans="23:23">
       <c r="W209" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="210" spans="23:23">
       <c r="W210" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="211" spans="23:23">
       <c r="W211" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="212" spans="23:23">
       <c r="W212" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="213" spans="23:23">
       <c r="W213" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="214" spans="23:23">
       <c r="W214" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="215" spans="23:23">
       <c r="W215" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="216" spans="23:23">
       <c r="W216" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="217" spans="23:23">
       <c r="W217" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="218" spans="23:23">
       <c r="W218" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="219" spans="23:23">
       <c r="W219" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="220" spans="23:23">
       <c r="W220" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="221" spans="23:23">
       <c r="W221" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="222" spans="23:23">
       <c r="W222" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="223" spans="23:23">
       <c r="W223" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="224" spans="23:23">
       <c r="W224" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="225" spans="23:23">
       <c r="W225" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="226" spans="23:23">
       <c r="W226" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="227" spans="23:23">
       <c r="W227" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="228" spans="23:23">
       <c r="W228" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="229" spans="23:23">
       <c r="W229" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="230" spans="23:23">
       <c r="W230" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="231" spans="23:23">
       <c r="W231" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="232" spans="23:23">
       <c r="W232" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="233" spans="23:23">
       <c r="W233" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="234" spans="23:23">
       <c r="W234" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="235" spans="23:23">
       <c r="W235" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="236" spans="23:23">
       <c r="W236" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="237" spans="23:23">
       <c r="W237" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="238" spans="23:23">
       <c r="W238" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="239" spans="23:23">
       <c r="W239" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="240" spans="23:23">
       <c r="W240" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="241" spans="23:23">
       <c r="W241" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="242" spans="23:23">
       <c r="W242" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="243" spans="23:23">
       <c r="W243" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="244" spans="23:23">
       <c r="W244" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="245" spans="23:23">
       <c r="W245" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="246" spans="23:23">
       <c r="W246" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="247" spans="23:23">
       <c r="W247" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="248" spans="23:23">
       <c r="W248" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="249" spans="23:23">
       <c r="W249" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="250" spans="23:23">
       <c r="W250" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="251" spans="23:23">
       <c r="W251" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="252" spans="23:23">
       <c r="W252" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="253" spans="23:23">
       <c r="W253" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="254" spans="23:23">
       <c r="W254" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="255" spans="23:23">
       <c r="W255" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="256" spans="23:23">
       <c r="W256" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="257" spans="23:23">
       <c r="W257" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="258" spans="23:23">
       <c r="W258" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="259" spans="23:23">
       <c r="W259" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="260" spans="23:23">
       <c r="W260" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="261" spans="23:23">
       <c r="W261" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="262" spans="23:23">
       <c r="W262" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="263" spans="23:23">
       <c r="W263" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="264" spans="23:23">
       <c r="W264" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="265" spans="23:23">
       <c r="W265" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="266" spans="23:23">
       <c r="W266" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="267" spans="23:23">
       <c r="W267" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="268" spans="23:23">
       <c r="W268" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="269" spans="23:23">
       <c r="W269" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="270" spans="23:23">
       <c r="W270" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="271" spans="23:23">
       <c r="W271" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="272" spans="23:23">
       <c r="W272" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="273" spans="23:23">
       <c r="W273" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="274" spans="23:23">
       <c r="W274" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="275" spans="23:23">
       <c r="W275" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="276" spans="23:23">
       <c r="W276" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="277" spans="23:23">
       <c r="W277" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="278" spans="23:23">
       <c r="W278" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="279" spans="23:23">
       <c r="W279" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="280" spans="23:23">
       <c r="W280" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="281" spans="23:23">
       <c r="W281" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="282" spans="23:23">
       <c r="W282" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="283" spans="23:23">
       <c r="W283" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="284" spans="23:23">
       <c r="W284" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="285" spans="23:23">
       <c r="W285" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="286" spans="23:23">
       <c r="W286" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="287" spans="23:23">
       <c r="W287" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="288" spans="23:23">
       <c r="W288" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="289" spans="23:23">
       <c r="W289" t="s">
-        <v>606</v>
+        <v>608</v>
+      </c>
+    </row>
+    <row r="290" spans="23:23">
+      <c r="W290" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="291" spans="23:23">
+      <c r="W291" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="292" spans="23:23">
+      <c r="W292" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="293" spans="23:23">
+      <c r="W293" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="294" spans="23:23">
+      <c r="W294" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000036/metadata_template_ERC000036.xlsx
+++ b/templates/ERC000036/metadata_template_ERC000036.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$W$1:$W$294</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="investigationtype">'cv_sample'!$N$1:$N$12</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="631">
   <si>
     <t>alias</t>
   </si>
@@ -728,6 +728,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -2451,7 +2454,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2495,7 +2498,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2522,7 +2525,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3259,6 +3262,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3280,27 +3288,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3320,122 +3328,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -3459,180 +3467,180 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -3655,1508 +3663,1508 @@
   <sheetData>
     <row r="1" spans="14:23">
       <c r="N1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="W1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="14:23">
       <c r="N2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="W2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="14:23">
       <c r="N3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="W3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="14:23">
       <c r="N4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="W4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="14:23">
       <c r="N5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="W5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="14:23">
       <c r="N6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="W6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="14:23">
       <c r="N7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="W7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" spans="14:23">
       <c r="N8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="W8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" spans="14:23">
       <c r="N9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="W9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" spans="14:23">
       <c r="N10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="W10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="14:23">
       <c r="N11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="W11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="14:23">
       <c r="N12" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="W12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" spans="14:23">
       <c r="W13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="14" spans="14:23">
       <c r="W14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="15" spans="14:23">
       <c r="W15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16" spans="14:23">
       <c r="W16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="23:23">
       <c r="W17" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="23:23">
       <c r="W18" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" spans="23:23">
       <c r="W19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20" spans="23:23">
       <c r="W20" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="23:23">
       <c r="W21" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="22" spans="23:23">
       <c r="W22" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23" spans="23:23">
       <c r="W23" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="24" spans="23:23">
       <c r="W24" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="25" spans="23:23">
       <c r="W25" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" spans="23:23">
       <c r="W26" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="27" spans="23:23">
       <c r="W27" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="28" spans="23:23">
       <c r="W28" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="23:23">
       <c r="W29" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" spans="23:23">
       <c r="W30" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" spans="23:23">
       <c r="W31" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" spans="23:23">
       <c r="W32" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="33" spans="23:23">
       <c r="W33" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="34" spans="23:23">
       <c r="W34" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="35" spans="23:23">
       <c r="W35" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36" spans="23:23">
       <c r="W36" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="37" spans="23:23">
       <c r="W37" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38" spans="23:23">
       <c r="W38" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="39" spans="23:23">
       <c r="W39" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="40" spans="23:23">
       <c r="W40" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41" spans="23:23">
       <c r="W41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="42" spans="23:23">
       <c r="W42" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="43" spans="23:23">
       <c r="W43" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="44" spans="23:23">
       <c r="W44" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="45" spans="23:23">
       <c r="W45" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="46" spans="23:23">
       <c r="W46" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="47" spans="23:23">
       <c r="W47" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="48" spans="23:23">
       <c r="W48" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="49" spans="23:23">
       <c r="W49" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="50" spans="23:23">
       <c r="W50" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="51" spans="23:23">
       <c r="W51" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="52" spans="23:23">
       <c r="W52" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="53" spans="23:23">
       <c r="W53" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="54" spans="23:23">
       <c r="W54" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="55" spans="23:23">
       <c r="W55" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="56" spans="23:23">
       <c r="W56" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="57" spans="23:23">
       <c r="W57" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="58" spans="23:23">
       <c r="W58" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="59" spans="23:23">
       <c r="W59" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="60" spans="23:23">
       <c r="W60" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="61" spans="23:23">
       <c r="W61" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="62" spans="23:23">
       <c r="W62" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="63" spans="23:23">
       <c r="W63" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="64" spans="23:23">
       <c r="W64" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="65" spans="23:23">
       <c r="W65" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="66" spans="23:23">
       <c r="W66" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="67" spans="23:23">
       <c r="W67" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="68" spans="23:23">
       <c r="W68" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="69" spans="23:23">
       <c r="W69" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="70" spans="23:23">
       <c r="W70" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="71" spans="23:23">
       <c r="W71" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="72" spans="23:23">
       <c r="W72" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="73" spans="23:23">
       <c r="W73" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="74" spans="23:23">
       <c r="W74" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="75" spans="23:23">
       <c r="W75" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="76" spans="23:23">
       <c r="W76" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="77" spans="23:23">
       <c r="W77" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="78" spans="23:23">
       <c r="W78" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="79" spans="23:23">
       <c r="W79" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="80" spans="23:23">
       <c r="W80" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="81" spans="23:23">
       <c r="W81" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="82" spans="23:23">
       <c r="W82" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="83" spans="23:23">
       <c r="W83" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="84" spans="23:23">
       <c r="W84" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="85" spans="23:23">
       <c r="W85" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="86" spans="23:23">
       <c r="W86" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="87" spans="23:23">
       <c r="W87" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="88" spans="23:23">
       <c r="W88" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="89" spans="23:23">
       <c r="W89" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="23:23">
       <c r="W90" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="91" spans="23:23">
       <c r="W91" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="92" spans="23:23">
       <c r="W92" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="93" spans="23:23">
       <c r="W93" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="94" spans="23:23">
       <c r="W94" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="95" spans="23:23">
       <c r="W95" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="96" spans="23:23">
       <c r="W96" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="97" spans="23:23">
       <c r="W97" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="98" spans="23:23">
       <c r="W98" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="99" spans="23:23">
       <c r="W99" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="100" spans="23:23">
       <c r="W100" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="101" spans="23:23">
       <c r="W101" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="102" spans="23:23">
       <c r="W102" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="103" spans="23:23">
       <c r="W103" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="104" spans="23:23">
       <c r="W104" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="105" spans="23:23">
       <c r="W105" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="106" spans="23:23">
       <c r="W106" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="107" spans="23:23">
       <c r="W107" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="108" spans="23:23">
       <c r="W108" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="109" spans="23:23">
       <c r="W109" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="110" spans="23:23">
       <c r="W110" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="111" spans="23:23">
       <c r="W111" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="112" spans="23:23">
       <c r="W112" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="113" spans="23:23">
       <c r="W113" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="114" spans="23:23">
       <c r="W114" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="115" spans="23:23">
       <c r="W115" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="116" spans="23:23">
       <c r="W116" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="117" spans="23:23">
       <c r="W117" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="118" spans="23:23">
       <c r="W118" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="119" spans="23:23">
       <c r="W119" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="120" spans="23:23">
       <c r="W120" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="121" spans="23:23">
       <c r="W121" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="122" spans="23:23">
       <c r="W122" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="123" spans="23:23">
       <c r="W123" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="124" spans="23:23">
       <c r="W124" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="125" spans="23:23">
       <c r="W125" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="126" spans="23:23">
       <c r="W126" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="127" spans="23:23">
       <c r="W127" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="128" spans="23:23">
       <c r="W128" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="129" spans="23:23">
       <c r="W129" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="130" spans="23:23">
       <c r="W130" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="131" spans="23:23">
       <c r="W131" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="132" spans="23:23">
       <c r="W132" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="133" spans="23:23">
       <c r="W133" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="134" spans="23:23">
       <c r="W134" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="135" spans="23:23">
       <c r="W135" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="136" spans="23:23">
       <c r="W136" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="137" spans="23:23">
       <c r="W137" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="138" spans="23:23">
       <c r="W138" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="139" spans="23:23">
       <c r="W139" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="140" spans="23:23">
       <c r="W140" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="141" spans="23:23">
       <c r="W141" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="142" spans="23:23">
       <c r="W142" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="143" spans="23:23">
       <c r="W143" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="144" spans="23:23">
       <c r="W144" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="145" spans="23:23">
       <c r="W145" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="146" spans="23:23">
       <c r="W146" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="147" spans="23:23">
       <c r="W147" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="148" spans="23:23">
       <c r="W148" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="149" spans="23:23">
       <c r="W149" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="150" spans="23:23">
       <c r="W150" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="151" spans="23:23">
       <c r="W151" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="152" spans="23:23">
       <c r="W152" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="153" spans="23:23">
       <c r="W153" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="154" spans="23:23">
       <c r="W154" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="155" spans="23:23">
       <c r="W155" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="156" spans="23:23">
       <c r="W156" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="157" spans="23:23">
       <c r="W157" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="158" spans="23:23">
       <c r="W158" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="159" spans="23:23">
       <c r="W159" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="160" spans="23:23">
       <c r="W160" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="161" spans="23:23">
       <c r="W161" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="162" spans="23:23">
       <c r="W162" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="163" spans="23:23">
       <c r="W163" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="164" spans="23:23">
       <c r="W164" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="165" spans="23:23">
       <c r="W165" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="166" spans="23:23">
       <c r="W166" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="167" spans="23:23">
       <c r="W167" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="168" spans="23:23">
       <c r="W168" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="169" spans="23:23">
       <c r="W169" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="170" spans="23:23">
       <c r="W170" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="171" spans="23:23">
       <c r="W171" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="172" spans="23:23">
       <c r="W172" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="173" spans="23:23">
       <c r="W173" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="174" spans="23:23">
       <c r="W174" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="175" spans="23:23">
       <c r="W175" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="176" spans="23:23">
       <c r="W176" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="177" spans="23:23">
       <c r="W177" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="178" spans="23:23">
       <c r="W178" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="179" spans="23:23">
       <c r="W179" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="180" spans="23:23">
       <c r="W180" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="181" spans="23:23">
       <c r="W181" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="182" spans="23:23">
       <c r="W182" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="183" spans="23:23">
       <c r="W183" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="184" spans="23:23">
       <c r="W184" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="185" spans="23:23">
       <c r="W185" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="186" spans="23:23">
       <c r="W186" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="187" spans="23:23">
       <c r="W187" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="188" spans="23:23">
       <c r="W188" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="189" spans="23:23">
       <c r="W189" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="190" spans="23:23">
       <c r="W190" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="191" spans="23:23">
       <c r="W191" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="192" spans="23:23">
       <c r="W192" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="193" spans="23:23">
       <c r="W193" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="194" spans="23:23">
       <c r="W194" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="195" spans="23:23">
       <c r="W195" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="196" spans="23:23">
       <c r="W196" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="197" spans="23:23">
       <c r="W197" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="198" spans="23:23">
       <c r="W198" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="199" spans="23:23">
       <c r="W199" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="200" spans="23:23">
       <c r="W200" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="201" spans="23:23">
       <c r="W201" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="202" spans="23:23">
       <c r="W202" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="203" spans="23:23">
       <c r="W203" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="204" spans="23:23">
       <c r="W204" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="205" spans="23:23">
       <c r="W205" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="206" spans="23:23">
       <c r="W206" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="207" spans="23:23">
       <c r="W207" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="208" spans="23:23">
       <c r="W208" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="209" spans="23:23">
       <c r="W209" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="210" spans="23:23">
       <c r="W210" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="211" spans="23:23">
       <c r="W211" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="212" spans="23:23">
       <c r="W212" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="213" spans="23:23">
       <c r="W213" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="214" spans="23:23">
       <c r="W214" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="215" spans="23:23">
       <c r="W215" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="216" spans="23:23">
       <c r="W216" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="217" spans="23:23">
       <c r="W217" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="218" spans="23:23">
       <c r="W218" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="219" spans="23:23">
       <c r="W219" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="220" spans="23:23">
       <c r="W220" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="221" spans="23:23">
       <c r="W221" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="222" spans="23:23">
       <c r="W222" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="223" spans="23:23">
       <c r="W223" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="224" spans="23:23">
       <c r="W224" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="225" spans="23:23">
       <c r="W225" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="226" spans="23:23">
       <c r="W226" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="227" spans="23:23">
       <c r="W227" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="228" spans="23:23">
       <c r="W228" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="229" spans="23:23">
       <c r="W229" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="230" spans="23:23">
       <c r="W230" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="231" spans="23:23">
       <c r="W231" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="232" spans="23:23">
       <c r="W232" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="233" spans="23:23">
       <c r="W233" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="234" spans="23:23">
       <c r="W234" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="235" spans="23:23">
       <c r="W235" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="236" spans="23:23">
       <c r="W236" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="237" spans="23:23">
       <c r="W237" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="238" spans="23:23">
       <c r="W238" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="239" spans="23:23">
       <c r="W239" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="240" spans="23:23">
       <c r="W240" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="241" spans="23:23">
       <c r="W241" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="242" spans="23:23">
       <c r="W242" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="243" spans="23:23">
       <c r="W243" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="244" spans="23:23">
       <c r="W244" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="245" spans="23:23">
       <c r="W245" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="246" spans="23:23">
       <c r="W246" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="247" spans="23:23">
       <c r="W247" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="248" spans="23:23">
       <c r="W248" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="249" spans="23:23">
       <c r="W249" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="250" spans="23:23">
       <c r="W250" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="251" spans="23:23">
       <c r="W251" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="252" spans="23:23">
       <c r="W252" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="253" spans="23:23">
       <c r="W253" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="254" spans="23:23">
       <c r="W254" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="255" spans="23:23">
       <c r="W255" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="256" spans="23:23">
       <c r="W256" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="257" spans="23:23">
       <c r="W257" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="258" spans="23:23">
       <c r="W258" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="259" spans="23:23">
       <c r="W259" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="260" spans="23:23">
       <c r="W260" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="261" spans="23:23">
       <c r="W261" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="262" spans="23:23">
       <c r="W262" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="263" spans="23:23">
       <c r="W263" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="264" spans="23:23">
       <c r="W264" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="265" spans="23:23">
       <c r="W265" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="266" spans="23:23">
       <c r="W266" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="267" spans="23:23">
       <c r="W267" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="268" spans="23:23">
       <c r="W268" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="269" spans="23:23">
       <c r="W269" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="270" spans="23:23">
       <c r="W270" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="271" spans="23:23">
       <c r="W271" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="272" spans="23:23">
       <c r="W272" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="273" spans="23:23">
       <c r="W273" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="274" spans="23:23">
       <c r="W274" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="275" spans="23:23">
       <c r="W275" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="276" spans="23:23">
       <c r="W276" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="277" spans="23:23">
       <c r="W277" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="278" spans="23:23">
       <c r="W278" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="279" spans="23:23">
       <c r="W279" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="280" spans="23:23">
       <c r="W280" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="281" spans="23:23">
       <c r="W281" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="282" spans="23:23">
       <c r="W282" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="283" spans="23:23">
       <c r="W283" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="284" spans="23:23">
       <c r="W284" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="285" spans="23:23">
       <c r="W285" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="286" spans="23:23">
       <c r="W286" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="287" spans="23:23">
       <c r="W287" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="288" spans="23:23">
       <c r="W288" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="289" spans="23:23">
       <c r="W289" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="290" spans="23:23">
       <c r="W290" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="291" spans="23:23">
       <c r="W291" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="292" spans="23:23">
       <c r="W292" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="293" spans="23:23">
       <c r="W293" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="294" spans="23:23">
       <c r="W294" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>
